--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,11 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,6 +533,31 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -556,31 +586,46 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -610,31 +655,46 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -688,6 +748,21 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,6 +819,21 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,6 +888,21 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -826,31 +931,46 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -906,6 +1026,21 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -934,31 +1069,46 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -988,31 +1138,46 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1068,6 +1233,21 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1096,31 +1276,46 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1150,31 +1345,46 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1204,19 +1414,19 @@
         <v>32</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1225,9 +1435,24 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1258,31 +1483,46 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1338,6 +1578,21 @@
       <c r="P16" t="n">
         <v>100</v>
       </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1369,28 +1624,43 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>100</v>
+      </c>
+      <c r="R17" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -1420,31 +1690,46 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>100</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1500,6 +1785,21 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1554,6 +1854,21 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1582,31 +1897,46 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>100</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -1636,31 +1966,46 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -1690,31 +2035,46 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>100</v>
+      </c>
+      <c r="R23" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="n">
+        <v>100</v>
+      </c>
+      <c r="U23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -1770,6 +2130,21 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1801,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1813,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1822,7 +2197,22 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>100</v>
+      </c>
+      <c r="U25" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -1852,31 +2242,46 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="n">
+        <v>100</v>
+      </c>
+      <c r="U26" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1906,31 +2311,46 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" t="n">
+        <v>100</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1986,6 +2406,21 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2014,31 +2449,46 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" t="n">
+        <v>100</v>
+      </c>
+      <c r="T29" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -2094,6 +2544,21 @@
       <c r="P30" t="n">
         <v>100</v>
       </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T30" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2122,31 +2587,46 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>100</v>
+      </c>
+      <c r="S31" t="n">
+        <v>100</v>
+      </c>
+      <c r="T31" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -2176,31 +2656,46 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>100</v>
+      </c>
+      <c r="R32" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -2230,31 +2725,46 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -2284,31 +2794,46 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>100</v>
+      </c>
+      <c r="R34" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" t="n">
+        <v>100</v>
+      </c>
+      <c r="T34" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -2364,6 +2889,21 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2418,6 +2958,21 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2472,6 +3027,21 @@
       <c r="P37" t="n">
         <v>100</v>
       </c>
+      <c r="Q37" t="n">
+        <v>100</v>
+      </c>
+      <c r="R37" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2500,31 +3070,46 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>100</v>
+      </c>
+      <c r="R38" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" t="n">
+        <v>100</v>
+      </c>
+      <c r="T38" t="n">
+        <v>100</v>
+      </c>
+      <c r="U38" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -2554,30 +3139,45 @@
         <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P39" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>100</v>
+      </c>
+      <c r="R39" t="n">
+        <v>100</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="n">
+        <v>100</v>
+      </c>
+      <c r="U39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2634,6 +3234,21 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2688,6 +3303,21 @@
       <c r="P41" t="n">
         <v>100</v>
       </c>
+      <c r="Q41" t="n">
+        <v>100</v>
+      </c>
+      <c r="R41" t="n">
+        <v>100</v>
+      </c>
+      <c r="S41" t="n">
+        <v>100</v>
+      </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2716,31 +3346,46 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>100</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2770,31 +3415,46 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>100</v>
+      </c>
+      <c r="R43" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -2850,6 +3510,21 @@
       <c r="P44" t="n">
         <v>100</v>
       </c>
+      <c r="Q44" t="n">
+        <v>100</v>
+      </c>
+      <c r="R44" t="n">
+        <v>100</v>
+      </c>
+      <c r="S44" t="n">
+        <v>100</v>
+      </c>
+      <c r="T44" t="n">
+        <v>100</v>
+      </c>
+      <c r="U44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2878,31 +3553,46 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>100</v>
+      </c>
+      <c r="R45" t="n">
+        <v>100</v>
+      </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="n">
+        <v>100</v>
+      </c>
+      <c r="U45" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -2958,6 +3648,21 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2986,31 +3691,46 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>100</v>
+      </c>
+      <c r="R47" t="n">
+        <v>100</v>
+      </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="n">
+        <v>100</v>
+      </c>
+      <c r="U47" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -3043,28 +3763,43 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>100</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>100</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -3120,6 +3855,21 @@
       <c r="P49" t="n">
         <v>0</v>
       </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3174,6 +3924,21 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3228,6 +3993,21 @@
       <c r="P51" t="n">
         <v>100</v>
       </c>
+      <c r="Q51" t="n">
+        <v>100</v>
+      </c>
+      <c r="R51" t="n">
+        <v>100</v>
+      </c>
+      <c r="S51" t="n">
+        <v>100</v>
+      </c>
+      <c r="T51" t="n">
+        <v>100</v>
+      </c>
+      <c r="U51" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3256,31 +4036,46 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>100</v>
+      </c>
+      <c r="R52" t="n">
+        <v>100</v>
+      </c>
+      <c r="S52" t="n">
+        <v>100</v>
+      </c>
+      <c r="T52" t="n">
+        <v>100</v>
+      </c>
+      <c r="U52" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -3336,6 +4131,21 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3364,31 +4174,46 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>100</v>
+      </c>
+      <c r="R54" t="n">
+        <v>100</v>
+      </c>
+      <c r="S54" t="n">
+        <v>100</v>
+      </c>
+      <c r="T54" t="n">
+        <v>100</v>
+      </c>
+      <c r="U54" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -3418,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3430,19 +4255,34 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>100</v>
+      </c>
+      <c r="T55" t="n">
+        <v>100</v>
+      </c>
+      <c r="U55" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -3478,16 +4318,16 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -3496,6 +4336,21 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>100</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3526,31 +4381,46 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>100</v>
+      </c>
+      <c r="R57" t="n">
+        <v>100</v>
+      </c>
+      <c r="S57" t="n">
+        <v>100</v>
+      </c>
+      <c r="T57" t="n">
+        <v>100</v>
+      </c>
+      <c r="U57" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -3592,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3604,6 +4474,21 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>100</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3660,6 +4545,21 @@
       <c r="P59" t="n">
         <v>100</v>
       </c>
+      <c r="Q59" t="n">
+        <v>100</v>
+      </c>
+      <c r="R59" t="n">
+        <v>100</v>
+      </c>
+      <c r="S59" t="n">
+        <v>100</v>
+      </c>
+      <c r="T59" t="n">
+        <v>100</v>
+      </c>
+      <c r="U59" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3688,31 +4588,46 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>100</v>
+      </c>
+      <c r="R60" t="n">
+        <v>100</v>
+      </c>
+      <c r="S60" t="n">
+        <v>100</v>
+      </c>
+      <c r="T60" t="n">
+        <v>100</v>
+      </c>
+      <c r="U60" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -3742,31 +4657,46 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>100</v>
+      </c>
+      <c r="R61" t="n">
+        <v>100</v>
+      </c>
+      <c r="S61" t="n">
+        <v>100</v>
+      </c>
+      <c r="T61" t="n">
+        <v>100</v>
+      </c>
+      <c r="U61" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -3796,31 +4726,46 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>100</v>
+      </c>
+      <c r="R62" t="n">
+        <v>100</v>
+      </c>
+      <c r="S62" t="n">
+        <v>100</v>
+      </c>
+      <c r="T62" t="n">
+        <v>100</v>
+      </c>
+      <c r="U62" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -3876,6 +4821,21 @@
       <c r="P63" t="n">
         <v>100</v>
       </c>
+      <c r="Q63" t="n">
+        <v>100</v>
+      </c>
+      <c r="R63" t="n">
+        <v>100</v>
+      </c>
+      <c r="S63" t="n">
+        <v>100</v>
+      </c>
+      <c r="T63" t="n">
+        <v>100</v>
+      </c>
+      <c r="U63" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3904,31 +4864,46 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>100</v>
+      </c>
+      <c r="R64" t="n">
+        <v>100</v>
+      </c>
+      <c r="S64" t="n">
+        <v>100</v>
+      </c>
+      <c r="T64" t="n">
+        <v>100</v>
+      </c>
+      <c r="U64" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3964,25 +4939,40 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>100</v>
+      </c>
+      <c r="R65" t="n">
+        <v>100</v>
+      </c>
+      <c r="S65" t="n">
+        <v>100</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -4012,31 +5002,46 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>100</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>100</v>
+      </c>
+      <c r="T66" t="n">
+        <v>100</v>
+      </c>
+      <c r="U66" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -4066,31 +5071,46 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>100</v>
+      </c>
+      <c r="R67" t="n">
+        <v>100</v>
+      </c>
+      <c r="S67" t="n">
+        <v>100</v>
+      </c>
+      <c r="T67" t="n">
+        <v>100</v>
+      </c>
+      <c r="U67" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -4146,6 +5166,21 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4200,6 +5235,21 @@
       <c r="P69" t="n">
         <v>0</v>
       </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4228,31 +5278,46 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>100</v>
+      </c>
+      <c r="R70" t="n">
+        <v>100</v>
+      </c>
+      <c r="S70" t="n">
+        <v>100</v>
+      </c>
+      <c r="T70" t="n">
+        <v>100</v>
+      </c>
+      <c r="U70" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -4282,31 +5347,46 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>100</v>
+      </c>
+      <c r="R71" t="n">
+        <v>100</v>
+      </c>
+      <c r="S71" t="n">
+        <v>100</v>
+      </c>
+      <c r="T71" t="n">
+        <v>100</v>
+      </c>
+      <c r="U71" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -4362,6 +5442,21 @@
       <c r="P72" t="n">
         <v>100</v>
       </c>
+      <c r="Q72" t="n">
+        <v>100</v>
+      </c>
+      <c r="R72" t="n">
+        <v>100</v>
+      </c>
+      <c r="S72" t="n">
+        <v>100</v>
+      </c>
+      <c r="T72" t="n">
+        <v>100</v>
+      </c>
+      <c r="U72" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4416,6 +5511,21 @@
       <c r="P73" t="n">
         <v>0</v>
       </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4470,6 +5580,21 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4524,6 +5649,21 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4552,31 +5692,46 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>100</v>
+      </c>
+      <c r="R76" t="n">
+        <v>100</v>
+      </c>
+      <c r="S76" t="n">
+        <v>100</v>
+      </c>
+      <c r="T76" t="n">
+        <v>100</v>
+      </c>
+      <c r="U76" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -4632,6 +5787,21 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4660,31 +5830,46 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>100</v>
+      </c>
+      <c r="R78" t="n">
+        <v>100</v>
+      </c>
+      <c r="S78" t="n">
+        <v>100</v>
+      </c>
+      <c r="T78" t="n">
+        <v>100</v>
+      </c>
+      <c r="U78" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -4740,6 +5925,21 @@
       <c r="P79" t="n">
         <v>100</v>
       </c>
+      <c r="Q79" t="n">
+        <v>100</v>
+      </c>
+      <c r="R79" t="n">
+        <v>100</v>
+      </c>
+      <c r="S79" t="n">
+        <v>100</v>
+      </c>
+      <c r="T79" t="n">
+        <v>100</v>
+      </c>
+      <c r="U79" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4794,6 +5994,21 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4822,31 +6037,46 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>100</v>
+      </c>
+      <c r="R81" t="n">
+        <v>100</v>
+      </c>
+      <c r="S81" t="n">
+        <v>100</v>
+      </c>
+      <c r="T81" t="n">
+        <v>100</v>
+      </c>
+      <c r="U81" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -4876,31 +6106,46 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>100</v>
+      </c>
+      <c r="R82" t="n">
+        <v>100</v>
+      </c>
+      <c r="S82" t="n">
+        <v>100</v>
+      </c>
+      <c r="T82" t="n">
+        <v>100</v>
+      </c>
+      <c r="U82" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="83">
@@ -4933,28 +6178,43 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>100</v>
+      </c>
+      <c r="R83" t="n">
+        <v>100</v>
+      </c>
+      <c r="S83" t="n">
+        <v>100</v>
+      </c>
+      <c r="T83" t="n">
+        <v>100</v>
+      </c>
+      <c r="U83" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -4984,31 +6244,46 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>100</v>
+      </c>
+      <c r="R84" t="n">
+        <v>100</v>
+      </c>
+      <c r="S84" t="n">
+        <v>100</v>
+      </c>
+      <c r="T84" t="n">
+        <v>100</v>
+      </c>
+      <c r="U84" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -5038,31 +6313,46 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>100</v>
+      </c>
+      <c r="R85" t="n">
+        <v>100</v>
+      </c>
+      <c r="S85" t="n">
+        <v>100</v>
+      </c>
+      <c r="T85" t="n">
+        <v>100</v>
+      </c>
+      <c r="U85" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="86">
@@ -5101,13 +6391,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -5117,6 +6407,21 @@
       </c>
       <c r="P86" t="n">
         <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>100</v>
+      </c>
+      <c r="S86" t="n">
+        <v>100</v>
+      </c>
+      <c r="T86" t="n">
+        <v>100</v>
+      </c>
+      <c r="U86" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="87">
@@ -5146,31 +6451,46 @@
         <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>100</v>
+      </c>
+      <c r="R87" t="n">
+        <v>100</v>
+      </c>
+      <c r="S87" t="n">
+        <v>100</v>
+      </c>
+      <c r="T87" t="n">
+        <v>100</v>
+      </c>
+      <c r="U87" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="88">
@@ -5226,6 +6546,21 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5280,6 +6615,21 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5334,6 +6684,21 @@
       <c r="P90" t="n">
         <v>100</v>
       </c>
+      <c r="Q90" t="n">
+        <v>100</v>
+      </c>
+      <c r="R90" t="n">
+        <v>100</v>
+      </c>
+      <c r="S90" t="n">
+        <v>100</v>
+      </c>
+      <c r="T90" t="n">
+        <v>100</v>
+      </c>
+      <c r="U90" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5388,6 +6753,21 @@
       <c r="P91" t="n">
         <v>100</v>
       </c>
+      <c r="Q91" t="n">
+        <v>100</v>
+      </c>
+      <c r="R91" t="n">
+        <v>100</v>
+      </c>
+      <c r="S91" t="n">
+        <v>100</v>
+      </c>
+      <c r="T91" t="n">
+        <v>100</v>
+      </c>
+      <c r="U91" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5442,6 +6822,21 @@
       <c r="P92" t="n">
         <v>100</v>
       </c>
+      <c r="Q92" t="n">
+        <v>100</v>
+      </c>
+      <c r="R92" t="n">
+        <v>100</v>
+      </c>
+      <c r="S92" t="n">
+        <v>100</v>
+      </c>
+      <c r="T92" t="n">
+        <v>100</v>
+      </c>
+      <c r="U92" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5496,6 +6891,21 @@
       <c r="P93" t="n">
         <v>0</v>
       </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5530,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -5539,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -5549,6 +6959,21 @@
       </c>
       <c r="P94" t="n">
         <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>100</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>100</v>
+      </c>
+      <c r="U94" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -5578,31 +7003,46 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>100</v>
+      </c>
+      <c r="R95" t="n">
+        <v>100</v>
+      </c>
+      <c r="S95" t="n">
+        <v>100</v>
+      </c>
+      <c r="T95" t="n">
+        <v>100</v>
+      </c>
+      <c r="U95" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="96">
@@ -5632,31 +7072,46 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>100</v>
+      </c>
+      <c r="R96" t="n">
+        <v>100</v>
+      </c>
+      <c r="S96" t="n">
+        <v>100</v>
+      </c>
+      <c r="T96" t="n">
+        <v>100</v>
+      </c>
+      <c r="U96" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -5712,6 +7167,21 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5740,31 +7210,46 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>100</v>
+      </c>
+      <c r="R98" t="n">
+        <v>100</v>
+      </c>
+      <c r="S98" t="n">
+        <v>100</v>
+      </c>
+      <c r="T98" t="n">
+        <v>100</v>
+      </c>
+      <c r="U98" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="99">
@@ -5794,31 +7279,46 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>100</v>
+      </c>
+      <c r="R99" t="n">
+        <v>100</v>
+      </c>
+      <c r="S99" t="n">
+        <v>100</v>
+      </c>
+      <c r="T99" t="n">
+        <v>100</v>
+      </c>
+      <c r="U99" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="100">
@@ -5851,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5860,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -5872,6 +7372,21 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>100</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5928,6 +7443,21 @@
       <c r="P101" t="n">
         <v>100</v>
       </c>
+      <c r="Q101" t="n">
+        <v>100</v>
+      </c>
+      <c r="R101" t="n">
+        <v>100</v>
+      </c>
+      <c r="S101" t="n">
+        <v>100</v>
+      </c>
+      <c r="T101" t="n">
+        <v>100</v>
+      </c>
+      <c r="U101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5956,31 +7486,46 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>100</v>
+      </c>
+      <c r="S102" t="n">
+        <v>100</v>
+      </c>
+      <c r="T102" t="n">
+        <v>100</v>
+      </c>
+      <c r="U102" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -6010,31 +7555,46 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>100</v>
+      </c>
+      <c r="R103" t="n">
+        <v>100</v>
+      </c>
+      <c r="S103" t="n">
+        <v>100</v>
+      </c>
+      <c r="T103" t="n">
+        <v>100</v>
+      </c>
+      <c r="U103" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -6090,6 +7650,21 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6144,6 +7719,21 @@
       <c r="P105" t="n">
         <v>0</v>
       </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6172,31 +7762,46 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>100</v>
+      </c>
+      <c r="R106" t="n">
+        <v>100</v>
+      </c>
+      <c r="S106" t="n">
+        <v>100</v>
+      </c>
+      <c r="T106" t="n">
+        <v>100</v>
+      </c>
+      <c r="U106" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="107">
@@ -6226,31 +7831,46 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>100</v>
+      </c>
+      <c r="R107" t="n">
+        <v>100</v>
+      </c>
+      <c r="S107" t="n">
+        <v>100</v>
+      </c>
+      <c r="T107" t="n">
+        <v>100</v>
+      </c>
+      <c r="U107" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -6280,31 +7900,46 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>100</v>
+      </c>
+      <c r="R108" t="n">
+        <v>100</v>
+      </c>
+      <c r="S108" t="n">
+        <v>100</v>
+      </c>
+      <c r="T108" t="n">
+        <v>100</v>
+      </c>
+      <c r="U108" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="109">
@@ -6360,6 +7995,21 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6394,25 +8044,40 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>100</v>
+      </c>
+      <c r="R110" t="n">
+        <v>100</v>
+      </c>
+      <c r="S110" t="n">
+        <v>100</v>
+      </c>
+      <c r="T110" t="n">
+        <v>100</v>
+      </c>
+      <c r="U110" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="111">
@@ -6442,31 +8107,46 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>100</v>
+      </c>
+      <c r="R111" t="n">
+        <v>100</v>
+      </c>
+      <c r="S111" t="n">
+        <v>100</v>
+      </c>
+      <c r="T111" t="n">
+        <v>100</v>
+      </c>
+      <c r="U111" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="112">
@@ -6496,31 +8176,46 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>100</v>
+      </c>
+      <c r="R112" t="n">
+        <v>100</v>
+      </c>
+      <c r="S112" t="n">
+        <v>100</v>
+      </c>
+      <c r="T112" t="n">
+        <v>100</v>
+      </c>
+      <c r="U112" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="113">
@@ -6550,31 +8245,46 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>100</v>
+      </c>
+      <c r="R113" t="n">
+        <v>100</v>
+      </c>
+      <c r="S113" t="n">
+        <v>100</v>
+      </c>
+      <c r="T113" t="n">
+        <v>100</v>
+      </c>
+      <c r="U113" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="114">
@@ -6604,31 +8314,46 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>100</v>
+      </c>
+      <c r="R114" t="n">
+        <v>100</v>
+      </c>
+      <c r="S114" t="n">
+        <v>100</v>
+      </c>
+      <c r="T114" t="n">
+        <v>100</v>
+      </c>
+      <c r="U114" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="115">
@@ -6684,6 +8409,21 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6738,6 +8478,21 @@
       <c r="P116" t="n">
         <v>100</v>
       </c>
+      <c r="Q116" t="n">
+        <v>100</v>
+      </c>
+      <c r="R116" t="n">
+        <v>100</v>
+      </c>
+      <c r="S116" t="n">
+        <v>100</v>
+      </c>
+      <c r="T116" t="n">
+        <v>100</v>
+      </c>
+      <c r="U116" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6792,6 +8547,21 @@
       <c r="P117" t="n">
         <v>100</v>
       </c>
+      <c r="Q117" t="n">
+        <v>100</v>
+      </c>
+      <c r="R117" t="n">
+        <v>100</v>
+      </c>
+      <c r="S117" t="n">
+        <v>100</v>
+      </c>
+      <c r="T117" t="n">
+        <v>100</v>
+      </c>
+      <c r="U117" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6846,6 +8616,21 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6900,6 +8685,21 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6928,31 +8728,46 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>100</v>
+      </c>
+      <c r="R120" t="n">
+        <v>100</v>
+      </c>
+      <c r="S120" t="n">
+        <v>100</v>
+      </c>
+      <c r="T120" t="n">
+        <v>100</v>
+      </c>
+      <c r="U120" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="121">
@@ -6982,31 +8797,46 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>100</v>
+      </c>
+      <c r="R121" t="n">
+        <v>100</v>
+      </c>
+      <c r="S121" t="n">
+        <v>100</v>
+      </c>
+      <c r="T121" t="n">
+        <v>100</v>
+      </c>
+      <c r="U121" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="122">
@@ -7062,6 +8892,21 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7090,31 +8935,46 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>100</v>
+      </c>
+      <c r="R123" t="n">
+        <v>100</v>
+      </c>
+      <c r="S123" t="n">
+        <v>100</v>
+      </c>
+      <c r="T123" t="n">
+        <v>100</v>
+      </c>
+      <c r="U123" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="124">
@@ -7144,31 +9004,46 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>100</v>
+      </c>
+      <c r="R124" t="n">
+        <v>100</v>
+      </c>
+      <c r="S124" t="n">
+        <v>100</v>
+      </c>
+      <c r="T124" t="n">
+        <v>100</v>
+      </c>
+      <c r="U124" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="125">
@@ -7224,6 +9099,21 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7252,31 +9142,46 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>100</v>
+      </c>
+      <c r="R126" t="n">
+        <v>100</v>
+      </c>
+      <c r="S126" t="n">
+        <v>100</v>
+      </c>
+      <c r="T126" t="n">
+        <v>100</v>
+      </c>
+      <c r="U126" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="127">
@@ -7306,22 +9211,22 @@
         <v>35</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -7330,6 +9235,21 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>100</v>
+      </c>
+      <c r="U127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7363,28 +9283,43 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>100</v>
+      </c>
+      <c r="R128" t="n">
+        <v>100</v>
+      </c>
+      <c r="S128" t="n">
+        <v>100</v>
+      </c>
+      <c r="T128" t="n">
+        <v>100</v>
+      </c>
+      <c r="U128" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="129">
@@ -7414,31 +9349,46 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>100</v>
+      </c>
+      <c r="R129" t="n">
+        <v>100</v>
+      </c>
+      <c r="S129" t="n">
+        <v>100</v>
+      </c>
+      <c r="T129" t="n">
+        <v>100</v>
+      </c>
+      <c r="U129" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="130">
@@ -7468,31 +9418,46 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>100</v>
+      </c>
+      <c r="R130" t="n">
+        <v>100</v>
+      </c>
+      <c r="S130" t="n">
+        <v>100</v>
+      </c>
+      <c r="T130" t="n">
+        <v>100</v>
+      </c>
+      <c r="U130" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="131">
@@ -7522,31 +9487,46 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>100</v>
+      </c>
+      <c r="R131" t="n">
+        <v>100</v>
+      </c>
+      <c r="S131" t="n">
+        <v>100</v>
+      </c>
+      <c r="T131" t="n">
+        <v>100</v>
+      </c>
+      <c r="U131" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="132">
@@ -7602,6 +9582,21 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7630,31 +9625,46 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>100</v>
+      </c>
+      <c r="R133" t="n">
+        <v>100</v>
+      </c>
+      <c r="S133" t="n">
+        <v>100</v>
+      </c>
+      <c r="T133" t="n">
+        <v>100</v>
+      </c>
+      <c r="U133" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="134">
@@ -7696,19 +9706,34 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>100</v>
+      </c>
+      <c r="T134" t="n">
+        <v>100</v>
+      </c>
+      <c r="U134" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="135">
@@ -7738,30 +9763,45 @@
         <v>30</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P135" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>100</v>
+      </c>
+      <c r="R135" t="n">
+        <v>100</v>
+      </c>
+      <c r="S135" t="n">
+        <v>100</v>
+      </c>
+      <c r="T135" t="n">
+        <v>100</v>
+      </c>
+      <c r="U135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7818,6 +9858,21 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7872,6 +9927,21 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7926,6 +9996,21 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7954,31 +10039,46 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>100</v>
+      </c>
+      <c r="R139" t="n">
+        <v>100</v>
+      </c>
+      <c r="S139" t="n">
+        <v>100</v>
+      </c>
+      <c r="T139" t="n">
+        <v>100</v>
+      </c>
+      <c r="U139" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -8053,16 +10153,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E2" t="n">
         <v>189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -8080,16 +10180,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
         <v>154.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -8107,16 +10207,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1840</v>
+        <v>3240</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -8134,16 +10234,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
       <c r="E5" t="n">
-        <v>162.2</v>
+        <v>382.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
         <v>1.043</v>
@@ -8161,16 +10261,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="E6" t="n">
-        <v>160.7</v>
+        <v>349.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1.075</v>
@@ -8188,16 +10288,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E7" t="n">
-        <v>136.6</v>
+        <v>216.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -8215,16 +10315,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>750</v>
+        <v>1450</v>
       </c>
       <c r="F8" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -8242,16 +10342,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
         <v>397</v>
       </c>
       <c r="F9" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -8269,16 +10369,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="E10" t="n">
-        <v>164.7</v>
+        <v>231.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -8296,16 +10396,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>4.25</v>
+        <v>5.04</v>
       </c>
       <c r="E11" t="n">
-        <v>180.8</v>
+        <v>390.8</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>4.41</v>
       </c>
       <c r="G11" t="n">
         <v>1.007</v>
@@ -8323,16 +10423,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -8350,16 +10450,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
         <v>181</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -8377,16 +10477,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="F14" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -8404,16 +10504,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
         <v>117</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -8431,7 +10531,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -8458,16 +10558,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="E17" t="n">
-        <v>643</v>
+        <v>943</v>
       </c>
       <c r="F17" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -8485,16 +10585,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>514</v>
       </c>
       <c r="F18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -8512,16 +10612,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="E19" t="n">
-        <v>731.5</v>
+        <v>1256.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -8539,16 +10639,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>183.3</v>
+        <v>416.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -8566,16 +10666,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
         <v>154.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -8593,16 +10693,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E22" t="n">
         <v>124</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -8620,16 +10720,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E23" t="n">
         <v>124</v>
       </c>
       <c r="F23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -8647,13 +10747,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -8674,16 +10774,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1044</v>
+        <v>1744</v>
       </c>
       <c r="F25" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -8701,16 +10801,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E26" t="n">
         <v>200</v>
       </c>
       <c r="F26" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -8728,16 +10828,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D27" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="E27" t="n">
-        <v>143.2</v>
+        <v>209.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -8755,16 +10855,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>11.79</v>
+        <v>14.27</v>
       </c>
       <c r="E28" t="n">
-        <v>183.9</v>
+        <v>406</v>
       </c>
       <c r="F28" t="n">
-        <v>11.43</v>
+        <v>14.08</v>
       </c>
       <c r="G28" t="n">
         <v>0.796</v>
@@ -8782,16 +10882,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E29" t="n">
         <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -8809,7 +10909,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -8836,16 +10936,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="E31" t="n">
         <v>375.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -8863,16 +10963,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E32" t="n">
         <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -8890,16 +10990,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="E33" t="n">
         <v>241.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -8917,16 +11017,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D34" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E34" t="n">
         <v>191</v>
       </c>
       <c r="F34" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -8944,16 +11044,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>162.5</v>
+        <v>362.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>1.333</v>
@@ -8971,16 +11071,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="E36" t="n">
-        <v>174.4</v>
+        <v>361.9</v>
       </c>
       <c r="F36" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
         <v>1.333</v>
@@ -8998,7 +11098,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -9025,16 +11125,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="E38" t="n">
         <v>265</v>
       </c>
       <c r="F38" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -9052,16 +11152,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D39" t="n">
         <v>0.14</v>
       </c>
       <c r="E39" t="n">
-        <v>121</v>
+        <v>221</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -9079,16 +11179,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="E40" t="n">
-        <v>185.9</v>
+        <v>400.2</v>
       </c>
       <c r="F40" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="G40" t="n">
         <v>1.012</v>
@@ -9106,7 +11206,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -9133,16 +11233,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="E42" t="n">
-        <v>771</v>
+        <v>971</v>
       </c>
       <c r="F42" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -9160,16 +11260,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="E43" t="n">
-        <v>198.2</v>
+        <v>298.2</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -9187,7 +11287,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -9214,16 +11314,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="E45" t="n">
         <v>122.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -9241,16 +11341,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>4.49</v>
+        <v>5.56</v>
       </c>
       <c r="E46" t="n">
-        <v>186.2</v>
+        <v>420.3</v>
       </c>
       <c r="F46" t="n">
-        <v>4.34</v>
+        <v>5.48</v>
       </c>
       <c r="G46" t="n">
         <v>0.853</v>
@@ -9268,16 +11368,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E47" t="n">
         <v>124</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -9295,16 +11395,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="E48" t="n">
-        <v>732</v>
+        <v>1432</v>
       </c>
       <c r="F48" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -9322,16 +11422,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D49" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>750</v>
+        <v>1450</v>
       </c>
       <c r="F49" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -9349,16 +11449,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D50" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>750</v>
+        <v>1450</v>
       </c>
       <c r="F50" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -9376,7 +11476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -9403,16 +11503,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E52" t="n">
         <v>137</v>
       </c>
       <c r="F52" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -9430,16 +11530,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>425</v>
+        <v>775</v>
       </c>
       <c r="F53" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -9457,16 +11557,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D54" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E54" t="n">
         <v>121.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
@@ -9484,16 +11584,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E55" t="n">
-        <v>255.8</v>
+        <v>355.8</v>
       </c>
       <c r="F55" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -9511,16 +11611,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="E56" t="n">
-        <v>2480</v>
+        <v>4080</v>
       </c>
       <c r="F56" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -9538,16 +11638,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E57" t="n">
         <v>127</v>
       </c>
       <c r="F57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -9565,16 +11665,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="E58" t="n">
-        <v>221.6</v>
+        <v>461.6</v>
       </c>
       <c r="F58" t="n">
-        <v>0.29</v>
+        <v>0.55</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -9592,7 +11692,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -9619,16 +11719,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D60" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E60" t="n">
         <v>40</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -9646,16 +11746,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="E61" t="n">
         <v>347</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -9673,16 +11773,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D62" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E62" t="n">
         <v>68</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -9700,7 +11800,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -9727,16 +11827,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E64" t="n">
         <v>124</v>
       </c>
       <c r="F64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -9754,16 +11854,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D65" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="E65" t="n">
-        <v>191.2</v>
+        <v>341.2</v>
       </c>
       <c r="F65" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -9781,16 +11881,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="E66" t="n">
-        <v>134.2</v>
+        <v>159.2</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -9808,16 +11908,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E67" t="n">
         <v>69</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -9835,16 +11935,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>11.27</v>
+        <v>14.25</v>
       </c>
       <c r="E68" t="n">
-        <v>155.8</v>
+        <v>359</v>
       </c>
       <c r="F68" t="n">
-        <v>10.58</v>
+        <v>13.87</v>
       </c>
       <c r="G68" t="n">
         <v>0.879</v>
@@ -9862,16 +11962,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>13.59</v>
+        <v>14.71</v>
       </c>
       <c r="E69" t="n">
-        <v>292.5</v>
+        <v>577.3</v>
       </c>
       <c r="F69" t="n">
-        <v>12.43</v>
+        <v>14.08</v>
       </c>
       <c r="G69" t="n">
         <v>0.928</v>
@@ -9889,16 +11989,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E70" t="n">
         <v>309</v>
       </c>
       <c r="F70" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -9916,16 +12016,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D71" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E71" t="n">
         <v>220</v>
       </c>
       <c r="F71" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -9943,7 +12043,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -9970,16 +12070,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="E73" t="n">
-        <v>259.7</v>
+        <v>526.3</v>
       </c>
       <c r="F73" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="G73" t="n">
         <v>0.959</v>
@@ -9997,16 +12097,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D74" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="E74" t="n">
-        <v>213.2</v>
+        <v>463.2</v>
       </c>
       <c r="F74" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="G74" t="n">
         <v>1.089</v>
@@ -10024,16 +12124,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D75" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="E75" t="n">
-        <v>160.6</v>
+        <v>369.7</v>
       </c>
       <c r="F75" t="n">
-        <v>0.75</v>
+        <v>1.16</v>
       </c>
       <c r="G75" t="n">
         <v>1.188</v>
@@ -10051,16 +12151,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D76" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="E76" t="n">
         <v>319</v>
       </c>
       <c r="F76" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -10078,16 +12178,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D77" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>750</v>
+        <v>1450</v>
       </c>
       <c r="F77" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -10105,10 +12205,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D78" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E78" t="n">
         <v>190</v>
@@ -10132,7 +12232,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -10159,16 +12259,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>3.29</v>
+        <v>4.29</v>
       </c>
       <c r="E80" t="n">
-        <v>192.6</v>
+        <v>458.1</v>
       </c>
       <c r="F80" t="n">
-        <v>3.29</v>
+        <v>4.29</v>
       </c>
       <c r="G80" t="n">
         <v>0.84</v>
@@ -10186,16 +12286,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D81" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E81" t="n">
         <v>53</v>
       </c>
       <c r="F81" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -10213,16 +12313,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D82" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="E82" t="n">
         <v>238</v>
       </c>
       <c r="F82" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -10240,16 +12340,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="E83" t="n">
-        <v>670</v>
+        <v>870</v>
       </c>
       <c r="F83" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -10267,16 +12367,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E84" t="n">
         <v>47</v>
       </c>
       <c r="F84" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -10294,16 +12394,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D85" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E85" t="n">
         <v>115.5</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -10321,16 +12421,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="E86" t="n">
-        <v>1351</v>
+        <v>2051</v>
       </c>
       <c r="F86" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -10348,16 +12448,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D87" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="E87" t="n">
-        <v>374</v>
+        <v>474</v>
       </c>
       <c r="F87" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -10375,16 +12475,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="E88" t="n">
-        <v>122.2</v>
+        <v>245.3</v>
       </c>
       <c r="F88" t="n">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="G88" t="n">
         <v>1.776</v>
@@ -10402,13 +12502,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -10429,7 +12529,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -10456,7 +12556,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -10483,7 +12583,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -10510,13 +12610,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -10537,16 +12637,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>212.2</v>
+        <v>437.3</v>
       </c>
       <c r="F94" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
@@ -10564,16 +12664,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="E95" t="n">
         <v>482</v>
       </c>
       <c r="F95" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -10591,16 +12691,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="E96" t="n">
         <v>505</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -10618,16 +12718,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>9.5</v>
+        <v>12.14</v>
       </c>
       <c r="E97" t="n">
-        <v>171.8</v>
+        <v>400.5</v>
       </c>
       <c r="F97" t="n">
-        <v>9.42</v>
+        <v>12.1</v>
       </c>
       <c r="G97" t="n">
         <v>0.841</v>
@@ -10645,16 +12745,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E98" t="n">
         <v>126.5</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -10672,16 +12772,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D99" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E99" t="n">
         <v>62</v>
       </c>
       <c r="F99" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -10699,16 +12799,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D100" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F100" t="n">
         <v>0.65</v>
-      </c>
-      <c r="E100" t="n">
-        <v>552</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.59</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -10726,16 +12826,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D101" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -10753,13 +12853,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="E102" t="n">
-        <v>236</v>
+        <v>336</v>
       </c>
       <c r="F102" t="n">
         <v>0.14</v>
@@ -10780,16 +12880,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D103" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E103" t="n">
         <v>138</v>
       </c>
       <c r="F103" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -10807,16 +12907,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D104" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="E104" t="n">
-        <v>142.9</v>
+        <v>342.9</v>
       </c>
       <c r="F104" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -10834,16 +12934,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="E105" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="F105" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="G105" t="n">
         <v>0.986</v>
@@ -10861,16 +12961,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D106" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
       </c>
       <c r="F106" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -10888,16 +12988,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="E107" t="n">
         <v>457</v>
       </c>
       <c r="F107" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -10915,16 +13015,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D108" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E108" t="n">
         <v>201</v>
       </c>
       <c r="F108" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -10942,16 +13042,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>199.4</v>
+        <v>386.9</v>
       </c>
       <c r="F109" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="G109" t="n">
         <v>1.11</v>
@@ -10969,16 +13069,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D110" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E110" t="n">
-        <v>307</v>
+        <v>507</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -10996,16 +13096,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D111" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E111" t="n">
         <v>198</v>
       </c>
       <c r="F111" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -11023,16 +13123,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D112" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="E112" t="n">
         <v>238.5</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -11050,16 +13150,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D113" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E113" t="n">
         <v>304</v>
       </c>
       <c r="F113" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -11077,16 +13177,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D114" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E114" t="n">
         <v>212</v>
       </c>
       <c r="F114" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -11104,16 +13204,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>3.2</v>
+        <v>4.08</v>
       </c>
       <c r="E115" t="n">
-        <v>194.6</v>
+        <v>451.7</v>
       </c>
       <c r="F115" t="n">
-        <v>3.2</v>
+        <v>4.08</v>
       </c>
       <c r="G115" t="n">
         <v>0.8179999999999999</v>
@@ -11131,7 +13231,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -11158,7 +13258,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -11185,16 +13285,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="E118" t="n">
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -11212,13 +13312,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -11239,16 +13339,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D120" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="E120" t="n">
         <v>285</v>
       </c>
       <c r="F120" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -11266,16 +13366,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D121" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="E121" t="n">
         <v>239</v>
       </c>
       <c r="F121" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -11293,13 +13393,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -11320,16 +13420,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D123" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E123" t="n">
         <v>87</v>
       </c>
       <c r="F123" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -11347,16 +13447,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D124" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="E124" t="n">
-        <v>312.5</v>
+        <v>412.5</v>
       </c>
       <c r="F124" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -11374,16 +13474,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D125" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="E125" t="n">
-        <v>370.9</v>
+        <v>724.3</v>
       </c>
       <c r="F125" t="n">
-        <v>2.37</v>
+        <v>3.01</v>
       </c>
       <c r="G125" t="n">
         <v>2</v>
@@ -11401,16 +13501,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D126" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E126" t="n">
         <v>94</v>
       </c>
       <c r="F126" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -11428,16 +13528,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D127" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="E127" t="n">
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="F127" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="G127" t="n">
         <v>2</v>
@@ -11455,16 +13555,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D128" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E128" t="n">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="F128" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -11482,16 +13582,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D129" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E129" t="n">
         <v>129</v>
       </c>
       <c r="F129" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -11509,16 +13609,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D130" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="E130" t="n">
         <v>739</v>
       </c>
       <c r="F130" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -11536,16 +13636,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D131" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="E131" t="n">
         <v>156</v>
       </c>
       <c r="F131" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -11563,16 +13663,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>425</v>
+        <v>775</v>
       </c>
       <c r="F132" t="n">
-        <v>3.82</v>
+        <v>4.35</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -11590,16 +13690,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D133" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E133" t="n">
         <v>33</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -11617,16 +13717,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D134" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="E134" t="n">
-        <v>222.2</v>
+        <v>422.2</v>
       </c>
       <c r="F134" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="G134" t="n">
         <v>1.515</v>
@@ -11644,16 +13744,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D135" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="E135" t="n">
-        <v>238</v>
+        <v>338</v>
       </c>
       <c r="F135" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -11671,16 +13771,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D136" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="E136" t="n">
-        <v>387.7</v>
+        <v>771</v>
       </c>
       <c r="F136" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="G136" t="n">
         <v>1.103</v>
@@ -11698,16 +13798,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D137" t="n">
-        <v>9.1</v>
+        <v>12.21</v>
       </c>
       <c r="E137" t="n">
-        <v>159.4</v>
+        <v>390.3</v>
       </c>
       <c r="F137" t="n">
-        <v>9.09</v>
+        <v>12.21</v>
       </c>
       <c r="G137" t="n">
         <v>0.852</v>
@@ -11725,16 +13825,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D138" t="n">
-        <v>14.07</v>
+        <v>18.2</v>
       </c>
       <c r="E138" t="n">
-        <v>152.4</v>
+        <v>359.4</v>
       </c>
       <c r="F138" t="n">
-        <v>12.94</v>
+        <v>17.58</v>
       </c>
       <c r="G138" t="n">
         <v>0.9350000000000001</v>
@@ -11752,16 +13852,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D139" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="E139" t="n">
         <v>221.5</v>
       </c>
       <c r="F139" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -586,31 +586,31 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
         <v>100</v>
@@ -655,31 +655,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
         <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
         <v>50</v>
@@ -964,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1069,31 +1069,31 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
         <v>100</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
         <v>50</v>
@@ -1156,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1276,31 +1276,31 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
         <v>100</v>
@@ -1345,31 +1345,31 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
         <v>100</v>
@@ -1426,7 +1426,7 @@
         <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -1483,31 +1483,31 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
         <v>100</v>
@@ -1624,22 +1624,22 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1690,31 +1690,31 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="n">
         <v>100</v>
@@ -1897,31 +1897,31 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="n">
         <v>100</v>
@@ -1966,31 +1966,31 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="n">
         <v>100</v>
@@ -2035,31 +2035,31 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q23" t="n">
         <v>100</v>
@@ -2176,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
         <v>100</v>
@@ -2242,31 +2242,31 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
         <v>100</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>50</v>
@@ -2323,7 +2323,7 @@
         <v>50</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>50</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
         <v>50</v>
@@ -2341,16 +2341,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2449,31 +2449,31 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
         <v>100</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="n">
         <v>100</v>
@@ -2656,31 +2656,31 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q32" t="n">
         <v>100</v>
@@ -2725,31 +2725,31 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="n">
         <v>100</v>
@@ -2794,31 +2794,31 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="n">
         <v>100</v>
@@ -3070,31 +3070,31 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
@@ -3139,31 +3139,31 @@
         <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q39" t="n">
         <v>100</v>
@@ -3346,31 +3346,31 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q42" t="n">
         <v>100</v>
@@ -3415,28 +3415,28 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3553,31 +3553,31 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
@@ -3589,7 +3589,7 @@
         <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>100</v>
@@ -3691,31 +3691,31 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q47" t="n">
         <v>100</v>
@@ -3763,28 +3763,28 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q48" t="n">
         <v>100</v>
@@ -4036,31 +4036,31 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q52" t="n">
         <v>100</v>
@@ -4174,31 +4174,31 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
@@ -4207,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="S54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
         <v>100</v>
@@ -4243,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4255,19 +4255,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4318,16 +4318,16 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -4381,31 +4381,31 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q57" t="n">
         <v>100</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -4588,31 +4588,31 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q60" t="n">
         <v>100</v>
@@ -4657,31 +4657,31 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
@@ -4726,31 +4726,31 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q62" t="n">
         <v>100</v>
@@ -4864,31 +4864,31 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P64" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q64" t="n">
         <v>100</v>
@@ -4942,7 +4942,7 @@
         <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L65" t="n">
         <v>50</v>
@@ -4960,19 +4960,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>100</v>
       </c>
       <c r="S65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5014,13 +5014,13 @@
         <v>50</v>
       </c>
       <c r="L66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O66" t="n">
         <v>50</v>
@@ -5029,7 +5029,7 @@
         <v>50</v>
       </c>
       <c r="Q66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5071,31 +5071,31 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q67" t="n">
         <v>100</v>
@@ -5278,31 +5278,31 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q70" t="n">
         <v>100</v>
@@ -5347,31 +5347,31 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q71" t="n">
         <v>100</v>
@@ -5692,31 +5692,31 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q76" t="n">
         <v>100</v>
@@ -5830,31 +5830,31 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q78" t="n">
         <v>100</v>
@@ -6037,31 +6037,31 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P81" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q81" t="n">
         <v>100</v>
@@ -6106,31 +6106,31 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P82" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q82" t="n">
         <v>100</v>
@@ -6178,28 +6178,28 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q83" t="n">
         <v>100</v>
@@ -6244,31 +6244,31 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P84" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q84" t="n">
         <v>100</v>
@@ -6313,31 +6313,31 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q85" t="n">
         <v>100</v>
@@ -6391,13 +6391,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -6451,31 +6451,31 @@
         <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q87" t="n">
         <v>100</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -6970,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7003,31 +7003,31 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q95" t="n">
         <v>100</v>
@@ -7072,31 +7072,31 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q96" t="n">
         <v>100</v>
@@ -7210,31 +7210,31 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q98" t="n">
         <v>100</v>
@@ -7279,31 +7279,31 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P99" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q99" t="n">
         <v>100</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -7372,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -7486,31 +7486,31 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -7555,31 +7555,31 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q103" t="n">
         <v>100</v>
@@ -7762,31 +7762,31 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P106" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q106" t="n">
         <v>100</v>
@@ -7831,31 +7831,31 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P107" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q107" t="n">
         <v>100</v>
@@ -7900,31 +7900,31 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q108" t="n">
         <v>100</v>
@@ -8044,19 +8044,19 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -8107,31 +8107,31 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P111" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q111" t="n">
         <v>100</v>
@@ -8176,31 +8176,31 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q112" t="n">
         <v>100</v>
@@ -8245,31 +8245,31 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P113" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q113" t="n">
         <v>100</v>
@@ -8314,31 +8314,31 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P114" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q114" t="n">
         <v>100</v>
@@ -8728,31 +8728,31 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P120" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q120" t="n">
         <v>100</v>
@@ -8797,31 +8797,31 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q121" t="n">
         <v>100</v>
@@ -8935,31 +8935,31 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P123" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q123" t="n">
         <v>100</v>
@@ -9004,28 +9004,28 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O124" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -9142,31 +9142,31 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P126" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q126" t="n">
         <v>100</v>
@@ -9247,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -9283,28 +9283,28 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q128" t="n">
         <v>100</v>
@@ -9349,31 +9349,31 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P129" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q129" t="n">
         <v>100</v>
@@ -9418,31 +9418,31 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q130" t="n">
         <v>100</v>
@@ -9487,31 +9487,31 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P131" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q131" t="n">
         <v>100</v>
@@ -9625,31 +9625,31 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P133" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q133" t="n">
         <v>100</v>
@@ -9709,10 +9709,10 @@
         <v>50</v>
       </c>
       <c r="M134" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N134" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -9727,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -9763,31 +9763,31 @@
         <v>30</v>
       </c>
       <c r="H135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q135" t="n">
         <v>100</v>
@@ -10039,31 +10039,31 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P139" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q139" t="n">
         <v>100</v>
@@ -10156,13 +10156,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E2" t="n">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -10183,13 +10183,13 @@
         <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>154.5</v>
+        <v>106.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -10210,13 +10210,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="E4" t="n">
-        <v>3240</v>
+        <v>3193</v>
       </c>
       <c r="F4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -10237,13 +10237,13 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="E5" t="n">
-        <v>382.2</v>
+        <v>417.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="G5" t="n">
         <v>1.043</v>
@@ -10264,13 +10264,13 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="E6" t="n">
-        <v>349.6</v>
+        <v>360</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G6" t="n">
         <v>1.075</v>
@@ -10291,13 +10291,13 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="E7" t="n">
-        <v>216.6</v>
+        <v>331.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -10345,13 +10345,13 @@
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>397</v>
+        <v>191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -10372,13 +10372,13 @@
         <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="E10" t="n">
-        <v>231.3</v>
+        <v>358</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -10399,13 +10399,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="E11" t="n">
-        <v>390.8</v>
+        <v>388.2</v>
       </c>
       <c r="F11" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="G11" t="n">
         <v>1.007</v>
@@ -10426,13 +10426,13 @@
         <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -10453,13 +10453,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -10480,13 +10480,13 @@
         <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>477.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -10507,13 +10507,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -10561,13 +10561,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="E17" t="n">
-        <v>943</v>
+        <v>721</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -10588,13 +10588,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="E18" t="n">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="F18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -10615,13 +10615,13 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="E19" t="n">
-        <v>1256.5</v>
+        <v>1202.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -10669,13 +10669,13 @@
         <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>154.5</v>
+        <v>106.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -10696,13 +10696,13 @@
         <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -10723,13 +10723,13 @@
         <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -10777,13 +10777,13 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="E25" t="n">
-        <v>1744</v>
+        <v>1712</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -10804,13 +10804,13 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -10831,13 +10831,13 @@
         <v>31</v>
       </c>
       <c r="D27" t="n">
-        <v>0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>209.8</v>
+        <v>357.3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -10858,13 +10858,13 @@
         <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>14.27</v>
+        <v>12.32</v>
       </c>
       <c r="E28" t="n">
-        <v>406</v>
+        <v>350.5</v>
       </c>
       <c r="F28" t="n">
-        <v>14.08</v>
+        <v>12.13</v>
       </c>
       <c r="G28" t="n">
         <v>0.796</v>
@@ -10885,13 +10885,13 @@
         <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E29" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -10939,13 +10939,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="E31" t="n">
-        <v>375.5</v>
+        <v>206.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -10969,7 +10969,7 @@
         <v>0.01</v>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
         <v>0.01</v>
@@ -10993,13 +10993,13 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E33" t="n">
-        <v>241.5</v>
+        <v>147.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -11020,13 +11020,13 @@
         <v>31</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E34" t="n">
-        <v>191</v>
+        <v>86</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -11047,13 +11047,13 @@
         <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="E35" t="n">
-        <v>362.5</v>
+        <v>400</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G35" t="n">
         <v>1.333</v>
@@ -11074,13 +11074,13 @@
         <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="E36" t="n">
-        <v>361.9</v>
+        <v>366.4</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G36" t="n">
         <v>1.333</v>
@@ -11128,13 +11128,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E38" t="n">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="F38" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -11155,13 +11155,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="E39" t="n">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -11185,10 +11185,10 @@
         <v>1.81</v>
       </c>
       <c r="E40" t="n">
-        <v>400.2</v>
+        <v>399.9</v>
       </c>
       <c r="F40" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G40" t="n">
         <v>1.012</v>
@@ -11236,13 +11236,13 @@
         <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="E42" t="n">
-        <v>971</v>
+        <v>729</v>
       </c>
       <c r="F42" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -11266,10 +11266,10 @@
         <v>0.38</v>
       </c>
       <c r="E43" t="n">
-        <v>298.2</v>
+        <v>297.5</v>
       </c>
       <c r="F43" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -11317,13 +11317,13 @@
         <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E45" t="n">
-        <v>122.3</v>
+        <v>168.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -11344,13 +11344,13 @@
         <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>5.56</v>
+        <v>4.86</v>
       </c>
       <c r="E46" t="n">
-        <v>420.3</v>
+        <v>367.3</v>
       </c>
       <c r="F46" t="n">
-        <v>5.48</v>
+        <v>4.78</v>
       </c>
       <c r="G46" t="n">
         <v>0.853</v>
@@ -11371,13 +11371,13 @@
         <v>31</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E47" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -11398,13 +11398,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E48" t="n">
-        <v>1432</v>
+        <v>1388</v>
       </c>
       <c r="F48" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -11506,13 +11506,13 @@
         <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E52" t="n">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -11560,13 +11560,13 @@
         <v>31</v>
       </c>
       <c r="D54" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E54" t="n">
-        <v>121.7</v>
+        <v>137</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
@@ -11587,13 +11587,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="E55" t="n">
-        <v>355.8</v>
+        <v>333.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -11614,13 +11614,13 @@
         <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="E56" t="n">
-        <v>4080</v>
+        <v>3577</v>
       </c>
       <c r="F56" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -11641,13 +11641,13 @@
         <v>31</v>
       </c>
       <c r="D57" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E57" t="n">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -11668,13 +11668,13 @@
         <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="E58" t="n">
-        <v>461.6</v>
+        <v>633.4</v>
       </c>
       <c r="F58" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -11725,7 +11725,7 @@
         <v>0.01</v>
       </c>
       <c r="E60" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F60" t="n">
         <v>0.01</v>
@@ -11749,13 +11749,13 @@
         <v>31</v>
       </c>
       <c r="D61" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E61" t="n">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="F61" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -11776,13 +11776,13 @@
         <v>31</v>
       </c>
       <c r="D62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E62" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -11830,13 +11830,13 @@
         <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E64" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -11857,13 +11857,13 @@
         <v>31</v>
       </c>
       <c r="D65" t="n">
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="E65" t="n">
-        <v>341.2</v>
+        <v>528.2</v>
       </c>
       <c r="F65" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -11884,13 +11884,13 @@
         <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="E66" t="n">
-        <v>159.2</v>
+        <v>288.5</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -11911,13 +11911,13 @@
         <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E67" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -11938,13 +11938,13 @@
         <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>14.25</v>
+        <v>13.02</v>
       </c>
       <c r="E68" t="n">
-        <v>359</v>
+        <v>328.3</v>
       </c>
       <c r="F68" t="n">
-        <v>13.87</v>
+        <v>12.64</v>
       </c>
       <c r="G68" t="n">
         <v>0.879</v>
@@ -11965,13 +11965,13 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>14.71</v>
+        <v>13.56</v>
       </c>
       <c r="E69" t="n">
-        <v>577.3</v>
+        <v>532</v>
       </c>
       <c r="F69" t="n">
-        <v>14.08</v>
+        <v>12.92</v>
       </c>
       <c r="G69" t="n">
         <v>0.928</v>
@@ -11992,13 +11992,13 @@
         <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E70" t="n">
-        <v>309</v>
+        <v>142</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -12019,13 +12019,13 @@
         <v>31</v>
       </c>
       <c r="D71" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E71" t="n">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="F71" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -12076,7 +12076,7 @@
         <v>1.53</v>
       </c>
       <c r="E73" t="n">
-        <v>526.3</v>
+        <v>527</v>
       </c>
       <c r="F73" t="n">
         <v>1.4</v>
@@ -12103,10 +12103,10 @@
         <v>0.9</v>
       </c>
       <c r="E74" t="n">
-        <v>463.2</v>
+        <v>466.5</v>
       </c>
       <c r="F74" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G74" t="n">
         <v>1.089</v>
@@ -12127,13 +12127,13 @@
         <v>31</v>
       </c>
       <c r="D75" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="E75" t="n">
-        <v>369.7</v>
+        <v>410.9</v>
       </c>
       <c r="F75" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="G75" t="n">
         <v>1.188</v>
@@ -12154,13 +12154,13 @@
         <v>31</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E76" t="n">
-        <v>319</v>
+        <v>177</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -12208,13 +12208,13 @@
         <v>31</v>
       </c>
       <c r="D78" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E78" t="n">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -12262,13 +12262,13 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>4.29</v>
+        <v>3.79</v>
       </c>
       <c r="E80" t="n">
-        <v>458.1</v>
+        <v>405.2</v>
       </c>
       <c r="F80" t="n">
-        <v>4.29</v>
+        <v>3.79</v>
       </c>
       <c r="G80" t="n">
         <v>0.84</v>
@@ -12289,13 +12289,13 @@
         <v>31</v>
       </c>
       <c r="D81" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F81" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -12316,13 +12316,13 @@
         <v>31</v>
       </c>
       <c r="D82" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E82" t="n">
-        <v>238</v>
+        <v>161.5</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -12343,13 +12343,13 @@
         <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="E83" t="n">
-        <v>870</v>
+        <v>655</v>
       </c>
       <c r="F83" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -12370,13 +12370,13 @@
         <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E84" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="F84" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -12400,10 +12400,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E85" t="n">
-        <v>115.5</v>
+        <v>106.5</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -12424,13 +12424,13 @@
         <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>2051</v>
+        <v>1749</v>
       </c>
       <c r="F86" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -12451,13 +12451,13 @@
         <v>31</v>
       </c>
       <c r="D87" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="E87" t="n">
-        <v>474</v>
+        <v>378</v>
       </c>
       <c r="F87" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -12478,13 +12478,13 @@
         <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="E88" t="n">
-        <v>245.3</v>
+        <v>350.3</v>
       </c>
       <c r="F88" t="n">
-        <v>0.66</v>
+        <v>1.1</v>
       </c>
       <c r="G88" t="n">
         <v>1.776</v>
@@ -12640,13 +12640,13 @@
         <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="E94" t="n">
-        <v>437.3</v>
+        <v>654.8</v>
       </c>
       <c r="F94" t="n">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
@@ -12667,13 +12667,13 @@
         <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E95" t="n">
-        <v>482</v>
+        <v>244</v>
       </c>
       <c r="F95" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -12694,13 +12694,13 @@
         <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E96" t="n">
-        <v>505</v>
+        <v>245</v>
       </c>
       <c r="F96" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -12721,13 +12721,13 @@
         <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>12.14</v>
+        <v>11</v>
       </c>
       <c r="E97" t="n">
-        <v>400.5</v>
+        <v>362.8</v>
       </c>
       <c r="F97" t="n">
-        <v>12.1</v>
+        <v>10.96</v>
       </c>
       <c r="G97" t="n">
         <v>0.841</v>
@@ -12748,13 +12748,13 @@
         <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>126.5</v>
+        <v>105.5</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -12775,13 +12775,13 @@
         <v>31</v>
       </c>
       <c r="D99" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E99" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -12802,13 +12802,13 @@
         <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="E100" t="n">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="F100" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -12856,13 +12856,13 @@
         <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="E102" t="n">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="F102" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -12883,13 +12883,13 @@
         <v>31</v>
       </c>
       <c r="D103" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E103" t="n">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="F103" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -12937,13 +12937,13 @@
         <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E105" t="n">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G105" t="n">
         <v>0.986</v>
@@ -12964,13 +12964,13 @@
         <v>31</v>
       </c>
       <c r="D106" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E106" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -12991,13 +12991,13 @@
         <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="E107" t="n">
-        <v>457</v>
+        <v>183</v>
       </c>
       <c r="F107" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -13018,13 +13018,13 @@
         <v>31</v>
       </c>
       <c r="D108" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E108" t="n">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="F108" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -13048,7 +13048,7 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>386.9</v>
+        <v>386.5</v>
       </c>
       <c r="F109" t="n">
         <v>0.9</v>
@@ -13075,7 +13075,7 @@
         <v>0.33</v>
       </c>
       <c r="E110" t="n">
-        <v>507</v>
+        <v>516.5</v>
       </c>
       <c r="F110" t="n">
         <v>0.24</v>
@@ -13099,13 +13099,13 @@
         <v>31</v>
       </c>
       <c r="D111" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="E111" t="n">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="F111" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -13126,13 +13126,13 @@
         <v>31</v>
       </c>
       <c r="D112" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E112" t="n">
-        <v>238.5</v>
+        <v>136</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -13153,13 +13153,13 @@
         <v>31</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E113" t="n">
-        <v>304</v>
+        <v>153</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -13180,13 +13180,13 @@
         <v>31</v>
       </c>
       <c r="D114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E114" t="n">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="F114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -13207,13 +13207,13 @@
         <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>4.08</v>
+        <v>3.59</v>
       </c>
       <c r="E115" t="n">
-        <v>451.7</v>
+        <v>397.2</v>
       </c>
       <c r="F115" t="n">
-        <v>4.08</v>
+        <v>3.59</v>
       </c>
       <c r="G115" t="n">
         <v>0.8179999999999999</v>
@@ -13342,13 +13342,13 @@
         <v>31</v>
       </c>
       <c r="D120" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E120" t="n">
-        <v>285</v>
+        <v>117</v>
       </c>
       <c r="F120" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -13369,13 +13369,13 @@
         <v>31</v>
       </c>
       <c r="D121" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E121" t="n">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="F121" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -13423,13 +13423,13 @@
         <v>31</v>
       </c>
       <c r="D123" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E123" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F123" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -13450,13 +13450,13 @@
         <v>31</v>
       </c>
       <c r="D124" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="E124" t="n">
-        <v>412.5</v>
+        <v>355</v>
       </c>
       <c r="F124" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -13477,13 +13477,13 @@
         <v>31</v>
       </c>
       <c r="D125" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="E125" t="n">
-        <v>724.3</v>
+        <v>1085.3</v>
       </c>
       <c r="F125" t="n">
-        <v>3.01</v>
+        <v>4.75</v>
       </c>
       <c r="G125" t="n">
         <v>2</v>
@@ -13504,13 +13504,13 @@
         <v>31</v>
       </c>
       <c r="D126" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E126" t="n">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="F126" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -13531,13 +13531,13 @@
         <v>31</v>
       </c>
       <c r="D127" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="E127" t="n">
-        <v>302</v>
+        <v>431.4</v>
       </c>
       <c r="F127" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="G127" t="n">
         <v>2</v>
@@ -13561,7 +13561,7 @@
         <v>0.2</v>
       </c>
       <c r="E128" t="n">
-        <v>306</v>
+        <v>312.5</v>
       </c>
       <c r="F128" t="n">
         <v>0.08</v>
@@ -13585,13 +13585,13 @@
         <v>31</v>
       </c>
       <c r="D129" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E129" t="n">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="F129" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -13612,13 +13612,13 @@
         <v>31</v>
       </c>
       <c r="D130" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="E130" t="n">
-        <v>739</v>
+        <v>382</v>
       </c>
       <c r="F130" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -13639,13 +13639,13 @@
         <v>31</v>
       </c>
       <c r="D131" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E131" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="F131" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -13696,7 +13696,7 @@
         <v>0.01</v>
       </c>
       <c r="E133" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F133" t="n">
         <v>0.01</v>
@@ -13720,13 +13720,13 @@
         <v>31</v>
       </c>
       <c r="D134" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="E134" t="n">
-        <v>422.2</v>
+        <v>527.5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="G134" t="n">
         <v>1.515</v>
@@ -13747,13 +13747,13 @@
         <v>31</v>
       </c>
       <c r="D135" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="E135" t="n">
-        <v>338</v>
+        <v>284.5</v>
       </c>
       <c r="F135" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -13774,13 +13774,13 @@
         <v>31</v>
       </c>
       <c r="D136" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="E136" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="F136" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G136" t="n">
         <v>1.103</v>
@@ -13801,13 +13801,13 @@
         <v>31</v>
       </c>
       <c r="D137" t="n">
-        <v>12.21</v>
+        <v>11.35</v>
       </c>
       <c r="E137" t="n">
-        <v>390.3</v>
+        <v>362.8</v>
       </c>
       <c r="F137" t="n">
-        <v>12.21</v>
+        <v>11.35</v>
       </c>
       <c r="G137" t="n">
         <v>0.852</v>
@@ -13828,13 +13828,13 @@
         <v>31</v>
       </c>
       <c r="D138" t="n">
-        <v>18.2</v>
+        <v>17.36</v>
       </c>
       <c r="E138" t="n">
-        <v>359.4</v>
+        <v>342.7</v>
       </c>
       <c r="F138" t="n">
-        <v>17.58</v>
+        <v>16.74</v>
       </c>
       <c r="G138" t="n">
         <v>0.9350000000000001</v>
@@ -13855,13 +13855,13 @@
         <v>31</v>
       </c>
       <c r="D139" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="E139" t="n">
-        <v>221.5</v>
+        <v>142</v>
       </c>
       <c r="F139" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -640,19 +640,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>63.75</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>85.75</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -916,25 +916,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
         <v>100</v>
@@ -943,19 +943,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
@@ -964,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1147,10 +1147,10 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1168,10 +1168,10 @@
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1195,16 +1195,16 @@
         <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>67.25</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>51.65</v>
+        <v>57.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-178.5</v>
+        <v>-200</v>
       </c>
       <c r="G11" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1399,19 +1399,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56.5</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>50</v>
@@ -1468,19 +1468,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1675,19 +1675,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1882,19 +1882,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2227,19 +2227,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -2296,31 +2296,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
@@ -2329,28 +2329,28 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -2365,16 +2365,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="D28" t="n">
-        <v>99.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>85</v>
@@ -2434,19 +2434,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -2572,19 +2572,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -2710,19 +2710,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -3124,19 +3124,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -3193,19 +3193,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70.75</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>94.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3331,19 +3331,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -3568,7 +3568,7 @@
         <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
@@ -3589,7 +3589,7 @@
         <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" t="n">
         <v>100</v>
@@ -3607,19 +3607,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>92.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="D46" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>86.5</v>
+        <v>83.3</v>
       </c>
       <c r="G46" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -3676,19 +3676,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -3745,19 +3745,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -4021,19 +4021,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -4207,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T54" t="n">
         <v>100</v>
@@ -4231,16 +4231,16 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>28.5</v>
+        <v>50</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -4573,19 +4573,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
@@ -4711,19 +4711,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
@@ -4849,19 +4849,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
@@ -4918,19 +4918,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -4939,19 +4939,19 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
         <v>100</v>
       </c>
       <c r="L65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -4960,19 +4960,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R65" t="n">
         <v>100</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -4987,31 +4987,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
@@ -5023,13 +5023,13 @@
         <v>100</v>
       </c>
       <c r="O66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5056,19 +5056,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H67" t="n">
         <v>100</v>
@@ -5125,19 +5125,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>96.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>91.55000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="E68" t="n">
-        <v>83.65000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -5197,13 +5197,13 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>80.40000000000001</v>
+        <v>81.55000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-59.9</v>
+        <v>-60</v>
       </c>
       <c r="F69" t="n">
-        <v>92.2</v>
+        <v>93.5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -5263,19 +5263,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H70" t="n">
         <v>100</v>
@@ -5332,19 +5332,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -5470,19 +5470,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>49.7</v>
+        <v>33.3</v>
       </c>
       <c r="G73" t="n">
-        <v>74.5</v>
+        <v>50</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -5539,19 +5539,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F74" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -5608,16 +5608,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>68.5</v>
+        <v>100</v>
       </c>
       <c r="D75" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5677,19 +5677,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -5815,19 +5815,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
@@ -5953,19 +5953,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>99.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>76.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="E80" t="n">
-        <v>75.84999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="F80" t="n">
-        <v>40.3</v>
+        <v>33.3</v>
       </c>
       <c r="G80" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H81" t="n">
         <v>100</v>
@@ -6091,19 +6091,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H82" t="n">
         <v>100</v>
@@ -6160,19 +6160,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -6229,19 +6229,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H84" t="n">
         <v>100</v>
@@ -6298,19 +6298,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H85" t="n">
         <v>100</v>
@@ -6370,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -6436,19 +6436,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>100</v>
@@ -6505,16 +6505,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>65.25</v>
+        <v>50</v>
       </c>
       <c r="D88" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="E88" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -6919,19 +6919,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D94" t="n">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -6970,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -6988,19 +6988,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H95" t="n">
         <v>100</v>
@@ -7057,19 +7057,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -7126,19 +7126,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="D97" t="n">
-        <v>81.05</v>
+        <v>83.3</v>
       </c>
       <c r="E97" t="n">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="F97" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="G97" t="n">
-        <v>37.3</v>
+        <v>33.3</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -7195,19 +7195,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98" t="n">
         <v>100</v>
@@ -7264,19 +7264,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H99" t="n">
         <v>100</v>
@@ -7342,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G100" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -7471,19 +7471,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" t="n">
         <v>100</v>
@@ -7540,19 +7540,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -7747,19 +7747,19 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H106" t="n">
         <v>100</v>
@@ -7816,19 +7816,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H107" t="n">
         <v>100</v>
@@ -7885,19 +7885,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H108" t="n">
         <v>100</v>
@@ -7954,19 +7954,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>65.75</v>
+        <v>50</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>70.5</v>
+        <v>100</v>
       </c>
       <c r="F109" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -8023,19 +8023,19 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -8092,19 +8092,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H111" t="n">
         <v>100</v>
@@ -8161,19 +8161,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D112" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H112" t="n">
         <v>100</v>
@@ -8230,19 +8230,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -8299,19 +8299,19 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -8368,19 +8368,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>86.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="D115" t="n">
-        <v>84.25</v>
+        <v>75</v>
       </c>
       <c r="E115" t="n">
-        <v>63.3</v>
+        <v>66.7</v>
       </c>
       <c r="F115" t="n">
-        <v>79</v>
+        <v>66.7</v>
       </c>
       <c r="G115" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -8713,19 +8713,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H120" t="n">
         <v>100</v>
@@ -8782,19 +8782,19 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H121" t="n">
         <v>100</v>
@@ -8920,19 +8920,19 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -8989,19 +8989,19 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D124" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H124" t="n">
         <v>100</v>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -9127,19 +9127,19 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H126" t="n">
         <v>100</v>
@@ -9196,37 +9196,37 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E127" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -9235,7 +9235,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -9247,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -9265,19 +9265,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -9334,19 +9334,19 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -9412,10 +9412,10 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H130" t="n">
         <v>100</v>
@@ -9472,19 +9472,19 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H131" t="n">
         <v>100</v>
@@ -9610,19 +9610,19 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H133" t="n">
         <v>100</v>
@@ -9679,19 +9679,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>70.5</v>
+        <v>100</v>
       </c>
       <c r="D134" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -9706,7 +9706,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M134" t="n">
         <v>100</v>
@@ -9727,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135">
@@ -9748,19 +9748,19 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F135" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>100</v>
@@ -9820,13 +9820,13 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -9886,19 +9886,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="D137" t="n">
-        <v>75.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="F137" t="n">
         <v>63.6</v>
       </c>
       <c r="G137" t="n">
-        <v>78.5</v>
+        <v>75</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -9955,19 +9955,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>95.80000000000001</v>
+        <v>95</v>
       </c>
       <c r="D138" t="n">
-        <v>65.94999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E138" t="n">
-        <v>81.2</v>
+        <v>81.25</v>
       </c>
       <c r="F138" t="n">
-        <v>97.2</v>
+        <v>95.2</v>
       </c>
       <c r="G138" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -10024,19 +10024,19 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H139" t="n">
         <v>100</v>
@@ -10156,13 +10156,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -10183,13 +10183,13 @@
         <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>106.5</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -10210,13 +10210,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="E4" t="n">
-        <v>3193</v>
+        <v>3300</v>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -10237,16 +10237,16 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="E5" t="n">
-        <v>417.9</v>
+        <v>440</v>
       </c>
       <c r="F5" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="G5" t="n">
-        <v>1.043</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="6">
@@ -10264,16 +10264,16 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>360</v>
+        <v>322.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.075</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -10291,16 +10291,16 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.54</v>
+        <v>0.35</v>
       </c>
       <c r="E7" t="n">
-        <v>331.8</v>
+        <v>220</v>
       </c>
       <c r="F7" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -10345,13 +10345,13 @@
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -10372,16 +10372,16 @@
         <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>358</v>
+        <v>200</v>
       </c>
       <c r="F10" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -10399,16 +10399,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>5.01</v>
+        <v>4.94</v>
       </c>
       <c r="E11" t="n">
-        <v>388.2</v>
+        <v>382.5</v>
       </c>
       <c r="F11" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="G11" t="n">
-        <v>1.007</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -10426,13 +10426,13 @@
         <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -10453,13 +10453,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -10480,13 +10480,13 @@
         <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="E14" t="n">
-        <v>477.5</v>
+        <v>450</v>
       </c>
       <c r="F14" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -10507,13 +10507,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -10561,13 +10561,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>721</v>
+        <v>600</v>
       </c>
       <c r="F17" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -10588,13 +10588,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -10615,13 +10615,13 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="E19" t="n">
-        <v>1202.8</v>
+        <v>1175</v>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -10669,13 +10669,13 @@
         <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E21" t="n">
-        <v>106.5</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -10696,13 +10696,13 @@
         <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -10723,13 +10723,13 @@
         <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -10777,13 +10777,13 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="E25" t="n">
-        <v>1712</v>
+        <v>1800</v>
       </c>
       <c r="F25" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -10804,13 +10804,13 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -10831,16 +10831,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="E27" t="n">
-        <v>357.3</v>
+        <v>200</v>
       </c>
       <c r="F27" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -10885,13 +10885,13 @@
         <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -10939,13 +10939,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E31" t="n">
-        <v>206.5</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -10966,13 +10966,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -10993,13 +10993,13 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E33" t="n">
-        <v>147.5</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -11020,13 +11020,13 @@
         <v>31</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -11074,13 +11074,13 @@
         <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>366.4</v>
+        <v>362.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>1.333</v>
@@ -11128,13 +11128,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -11155,13 +11155,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E39" t="n">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F39" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -11182,16 +11182,16 @@
         <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="E40" t="n">
-        <v>399.9</v>
+        <v>407.1</v>
       </c>
       <c r="F40" t="n">
         <v>1.65</v>
       </c>
       <c r="G40" t="n">
-        <v>1.012</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="41">
@@ -11236,13 +11236,13 @@
         <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="E42" t="n">
-        <v>729</v>
+        <v>500</v>
       </c>
       <c r="F42" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -11263,13 +11263,13 @@
         <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="E43" t="n">
-        <v>297.5</v>
+        <v>275</v>
       </c>
       <c r="F43" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -11317,16 +11317,16 @@
         <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E45" t="n">
-        <v>168.3</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -11344,16 +11344,16 @@
         <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>4.86</v>
+        <v>4.74</v>
       </c>
       <c r="E46" t="n">
-        <v>367.3</v>
+        <v>358.5</v>
       </c>
       <c r="F46" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="G46" t="n">
-        <v>0.853</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="47">
@@ -11371,13 +11371,13 @@
         <v>31</v>
       </c>
       <c r="D47" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -11398,13 +11398,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="E48" t="n">
-        <v>1388</v>
+        <v>1200</v>
       </c>
       <c r="F48" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -11506,13 +11506,13 @@
         <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -11560,16 +11560,16 @@
         <v>31</v>
       </c>
       <c r="D54" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E54" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -11587,10 +11587,10 @@
         <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="E55" t="n">
-        <v>333.5</v>
+        <v>350</v>
       </c>
       <c r="F55" t="n">
         <v>0.19</v>
@@ -11614,13 +11614,13 @@
         <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="E56" t="n">
-        <v>3577</v>
+        <v>3700</v>
       </c>
       <c r="F56" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -11641,13 +11641,13 @@
         <v>31</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -11668,16 +11668,16 @@
         <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>633.4</v>
+        <v>580</v>
       </c>
       <c r="F58" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="59">
@@ -11722,13 +11722,13 @@
         <v>31</v>
       </c>
       <c r="D60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -11749,13 +11749,13 @@
         <v>31</v>
       </c>
       <c r="D61" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E61" t="n">
-        <v>199</v>
+        <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -11776,13 +11776,13 @@
         <v>31</v>
       </c>
       <c r="D62" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -11830,13 +11830,13 @@
         <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -11857,16 +11857,16 @@
         <v>31</v>
       </c>
       <c r="D65" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="E65" t="n">
-        <v>528.2</v>
+        <v>375</v>
       </c>
       <c r="F65" t="n">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -11884,16 +11884,16 @@
         <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="E66" t="n">
-        <v>288.5</v>
+        <v>125</v>
       </c>
       <c r="F66" t="n">
-        <v>0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -11911,13 +11911,13 @@
         <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -11938,13 +11938,13 @@
         <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>13.02</v>
+        <v>13.03</v>
       </c>
       <c r="E68" t="n">
-        <v>328.3</v>
+        <v>328.5</v>
       </c>
       <c r="F68" t="n">
-        <v>12.64</v>
+        <v>12.65</v>
       </c>
       <c r="G68" t="n">
         <v>0.879</v>
@@ -11965,16 +11965,16 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>13.56</v>
+        <v>13.48</v>
       </c>
       <c r="E69" t="n">
-        <v>532</v>
+        <v>529.1</v>
       </c>
       <c r="F69" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
       <c r="G69" t="n">
-        <v>0.928</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="70">
@@ -11992,13 +11992,13 @@
         <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -12019,13 +12019,13 @@
         <v>31</v>
       </c>
       <c r="D71" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -12073,16 +12073,16 @@
         <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="E73" t="n">
-        <v>527</v>
+        <v>577.8</v>
       </c>
       <c r="F73" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="G73" t="n">
-        <v>0.959</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="74">
@@ -12100,16 +12100,16 @@
         <v>31</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="E74" t="n">
-        <v>466.5</v>
+        <v>450</v>
       </c>
       <c r="F74" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="G74" t="n">
-        <v>1.089</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -12127,16 +12127,16 @@
         <v>31</v>
       </c>
       <c r="D75" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="E75" t="n">
-        <v>410.9</v>
+        <v>409.1</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G75" t="n">
-        <v>1.188</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="76">
@@ -12154,13 +12154,13 @@
         <v>31</v>
       </c>
       <c r="D76" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -12208,13 +12208,13 @@
         <v>31</v>
       </c>
       <c r="D78" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E78" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -12262,16 +12262,16 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="E80" t="n">
-        <v>405.2</v>
+        <v>403.4</v>
       </c>
       <c r="F80" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="G80" t="n">
-        <v>0.84</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="81">
@@ -12289,13 +12289,13 @@
         <v>31</v>
       </c>
       <c r="D81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -12316,13 +12316,13 @@
         <v>31</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E82" t="n">
-        <v>161.5</v>
+        <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -12343,13 +12343,13 @@
         <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="E83" t="n">
-        <v>655</v>
+        <v>600</v>
       </c>
       <c r="F83" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -12370,13 +12370,13 @@
         <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -12397,10 +12397,10 @@
         <v>31</v>
       </c>
       <c r="D85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E85" t="n">
-        <v>106.5</v>
+        <v>100</v>
       </c>
       <c r="F85" t="n">
         <v>-0.06</v>
@@ -12424,13 +12424,13 @@
         <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="E86" t="n">
-        <v>1749</v>
+        <v>1500</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -12451,13 +12451,13 @@
         <v>31</v>
       </c>
       <c r="D87" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E87" t="n">
-        <v>378</v>
+        <v>300</v>
       </c>
       <c r="F87" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -12478,16 +12478,16 @@
         <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="E88" t="n">
-        <v>350.3</v>
+        <v>361.5</v>
       </c>
       <c r="F88" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G88" t="n">
-        <v>1.776</v>
+        <v>1.857</v>
       </c>
     </row>
     <row r="89">
@@ -12640,16 +12640,16 @@
         <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="E94" t="n">
-        <v>654.8</v>
+        <v>500</v>
       </c>
       <c r="F94" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -12667,13 +12667,13 @@
         <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -12694,13 +12694,13 @@
         <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -12721,16 +12721,16 @@
         <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="E97" t="n">
-        <v>362.8</v>
+        <v>360.6</v>
       </c>
       <c r="F97" t="n">
-        <v>10.96</v>
+        <v>10.94</v>
       </c>
       <c r="G97" t="n">
-        <v>0.841</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="98">
@@ -12748,10 +12748,10 @@
         <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E98" t="n">
-        <v>105.5</v>
+        <v>100</v>
       </c>
       <c r="F98" t="n">
         <v>-0.06</v>
@@ -12775,13 +12775,13 @@
         <v>31</v>
       </c>
       <c r="D99" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -12802,13 +12802,13 @@
         <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="E100" t="n">
-        <v>1033</v>
+        <v>1100</v>
       </c>
       <c r="F100" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -12856,13 +12856,13 @@
         <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E102" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -12883,13 +12883,13 @@
         <v>31</v>
       </c>
       <c r="D103" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -12937,16 +12937,16 @@
         <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="E105" t="n">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="F105" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G105" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -12964,13 +12964,13 @@
         <v>31</v>
       </c>
       <c r="D106" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -12991,13 +12991,13 @@
         <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -13018,13 +13018,13 @@
         <v>31</v>
       </c>
       <c r="D108" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -13045,16 +13045,16 @@
         <v>31</v>
       </c>
       <c r="D109" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E109" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="F109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.9</v>
-      </c>
       <c r="G109" t="n">
-        <v>1.11</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="110">
@@ -13072,13 +13072,13 @@
         <v>31</v>
       </c>
       <c r="D110" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="E110" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
       <c r="F110" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -13099,13 +13099,13 @@
         <v>31</v>
       </c>
       <c r="D111" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -13126,13 +13126,13 @@
         <v>31</v>
       </c>
       <c r="D112" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E112" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -13153,13 +13153,13 @@
         <v>31</v>
       </c>
       <c r="D113" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -13180,13 +13180,13 @@
         <v>31</v>
       </c>
       <c r="D114" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -13207,16 +13207,16 @@
         <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="E115" t="n">
-        <v>397.2</v>
+        <v>389.3</v>
       </c>
       <c r="F115" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="116">
@@ -13342,13 +13342,13 @@
         <v>31</v>
       </c>
       <c r="D120" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -13369,13 +13369,13 @@
         <v>31</v>
       </c>
       <c r="D121" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -13423,13 +13423,13 @@
         <v>31</v>
       </c>
       <c r="D123" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -13450,13 +13450,13 @@
         <v>31</v>
       </c>
       <c r="D124" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="E124" t="n">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="F124" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -13477,16 +13477,16 @@
         <v>31</v>
       </c>
       <c r="D125" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
       <c r="E125" t="n">
-        <v>1085.3</v>
+        <v>1040</v>
       </c>
       <c r="F125" t="n">
-        <v>4.75</v>
+        <v>4.58</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="126">
@@ -13504,13 +13504,13 @@
         <v>31</v>
       </c>
       <c r="D126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -13531,16 +13531,16 @@
         <v>31</v>
       </c>
       <c r="D127" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="E127" t="n">
-        <v>431.4</v>
+        <v>300</v>
       </c>
       <c r="F127" t="n">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -13558,13 +13558,13 @@
         <v>31</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="E128" t="n">
-        <v>312.5</v>
+        <v>300</v>
       </c>
       <c r="F128" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -13585,13 +13585,13 @@
         <v>31</v>
       </c>
       <c r="D129" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -13612,13 +13612,13 @@
         <v>31</v>
       </c>
       <c r="D130" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E130" t="n">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="F130" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -13639,13 +13639,13 @@
         <v>31</v>
       </c>
       <c r="D131" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -13693,13 +13693,13 @@
         <v>31</v>
       </c>
       <c r="D133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -13720,16 +13720,16 @@
         <v>31</v>
       </c>
       <c r="D134" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="E134" t="n">
-        <v>527.5</v>
+        <v>375</v>
       </c>
       <c r="F134" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="G134" t="n">
-        <v>1.515</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -13747,13 +13747,13 @@
         <v>31</v>
       </c>
       <c r="D135" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="E135" t="n">
-        <v>284.5</v>
+        <v>250</v>
       </c>
       <c r="F135" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -13774,16 +13774,16 @@
         <v>31</v>
       </c>
       <c r="D136" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="E136" t="n">
-        <v>776</v>
+        <v>800</v>
       </c>
       <c r="F136" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G136" t="n">
-        <v>1.103</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="137">
@@ -13804,13 +13804,13 @@
         <v>11.35</v>
       </c>
       <c r="E137" t="n">
-        <v>362.8</v>
+        <v>362.9</v>
       </c>
       <c r="F137" t="n">
         <v>11.35</v>
       </c>
       <c r="G137" t="n">
-        <v>0.852</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="138">
@@ -13828,10 +13828,10 @@
         <v>31</v>
       </c>
       <c r="D138" t="n">
-        <v>17.36</v>
+        <v>17.39</v>
       </c>
       <c r="E138" t="n">
-        <v>342.7</v>
+        <v>343.3</v>
       </c>
       <c r="F138" t="n">
         <v>16.74</v>
@@ -13855,13 +13855,13 @@
         <v>31</v>
       </c>
       <c r="D139" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E139" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -1541,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="55">
@@ -1562,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="56">
@@ -3117,7 +3117,7 @@
         <v>17</v>
       </c>
       <c r="E134" t="n">
-        <v>94.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -3315,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="145">
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146">
@@ -4975,7 +4975,7 @@
         <v>4</v>
       </c>
       <c r="E228" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="229">
@@ -4996,7 +4996,7 @@
         <v>4</v>
       </c>
       <c r="E229" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="230">
@@ -5893,7 +5893,7 @@
         <v>20</v>
       </c>
       <c r="E274" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="275">
@@ -5914,7 +5914,7 @@
         <v>20</v>
       </c>
       <c r="E275" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="276">
@@ -47643,7 +47643,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -47664,7 +47664,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
@@ -48777,7 +48777,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -48798,7 +48798,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
@@ -49013,7 +49013,7 @@
         <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -49034,7 +49034,7 @@
         <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -49883,7 +49883,7 @@
         <v>15</v>
       </c>
       <c r="E134" t="n">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="135">
@@ -49904,7 +49904,7 @@
         <v>15</v>
       </c>
       <c r="E135" t="n">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="136">
@@ -50363,7 +50363,7 @@
         <v>4</v>
       </c>
       <c r="E158" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="159">
@@ -50384,7 +50384,7 @@
         <v>4</v>
       </c>
       <c r="E159" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="160">
@@ -51033,7 +51033,7 @@
         <v>12</v>
       </c>
       <c r="E192" t="n">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="193">
@@ -51054,7 +51054,7 @@
         <v>12</v>
       </c>
       <c r="E193" t="n">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="194">
@@ -51741,7 +51741,7 @@
         <v>4</v>
       </c>
       <c r="E228" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="229">
@@ -51762,7 +51762,7 @@
         <v>4</v>
       </c>
       <c r="E229" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="230">
@@ -52617,7 +52617,7 @@
         <v>13</v>
       </c>
       <c r="E272" t="n">
-        <v>76.90000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="273">
@@ -52638,7 +52638,7 @@
         <v>13</v>
       </c>
       <c r="E273" t="n">
-        <v>76.90000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="274">
@@ -52659,7 +52659,7 @@
         <v>17</v>
       </c>
       <c r="E274" t="n">
-        <v>64.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -52680,7 +52680,7 @@
         <v>17</v>
       </c>
       <c r="E275" t="n">
-        <v>64.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -57605,7 +57605,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="55">
@@ -57626,7 +57626,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="56">
@@ -59219,7 +59219,7 @@
         <v>5</v>
       </c>
       <c r="E136" t="n">
-        <v>-60</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="137">
@@ -59240,7 +59240,7 @@
         <v>5</v>
       </c>
       <c r="E137" t="n">
-        <v>-60</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="138">
@@ -59657,7 +59657,7 @@
         <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="159">
@@ -59678,7 +59678,7 @@
         <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160">
@@ -61039,7 +61039,7 @@
         <v>3</v>
       </c>
       <c r="E228" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="229">
@@ -61060,7 +61060,7 @@
         <v>3</v>
       </c>
       <c r="E229" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230">
@@ -61913,7 +61913,7 @@
         <v>11</v>
       </c>
       <c r="E272" t="n">
-        <v>81.8</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="273">
@@ -61934,7 +61934,7 @@
         <v>11</v>
       </c>
       <c r="E273" t="n">
-        <v>81.8</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -62266,7 +62266,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>-200</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -62605,7 +62605,7 @@
         <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -62957,7 +62957,7 @@
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="47">
@@ -63391,7 +63391,7 @@
         <v>13</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -63633,7 +63633,7 @@
         <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
@@ -63964,7 +63964,7 @@
         <v>9</v>
       </c>
       <c r="E97" t="n">
-        <v>22.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="98">
@@ -64316,7 +64316,7 @@
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116">
@@ -64750,7 +64750,7 @@
         <v>11</v>
       </c>
       <c r="E137" t="n">
-        <v>63.6</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="138">
@@ -65038,7 +65038,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -65723,7 +65723,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
@@ -66155,7 +66155,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69">
@@ -66728,7 +66728,7 @@
         <v>9</v>
       </c>
       <c r="E97" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -67082,7 +67082,7 @@
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116">
@@ -67518,7 +67518,7 @@
         <v>12</v>
       </c>
       <c r="E137" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138">
@@ -67539,7 +67539,7 @@
         <v>14</v>
       </c>
       <c r="E138" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="139">

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -56200,13 +56200,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="E4" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="F4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -56929,13 +56929,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -57955,16 +57955,16 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>13.48</v>
+        <v>13</v>
       </c>
       <c r="E69" t="n">
-        <v>529.1</v>
+        <v>428.7</v>
       </c>
       <c r="F69" t="n">
-        <v>12.9</v>
+        <v>12.42</v>
       </c>
       <c r="G69" t="n">
-        <v>0.919</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="70">
@@ -68752,10 +68752,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -69319,10 +69319,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -70117,10 +70117,10 @@
         <v>16</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -7429,13 +7429,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -8185,13 +8185,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135">
@@ -9151,13 +9151,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
@@ -9613,13 +9613,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -10201,13 +10201,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -10327,13 +10327,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
@@ -11083,13 +11083,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -11503,13 +11503,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -12853,13 +12853,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
@@ -14029,13 +14029,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -14533,13 +14533,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -14953,13 +14953,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135">
@@ -14995,13 +14995,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137">
@@ -15457,13 +15457,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -16171,13 +16171,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193">
@@ -16675,13 +16675,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -17347,13 +17347,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -17851,13 +17851,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -17893,13 +17893,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275">
@@ -18151,13 +18151,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -18193,13 +18193,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -18403,13 +18403,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -18739,13 +18739,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -18991,13 +18991,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -19117,13 +19117,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -19411,13 +19411,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -19453,13 +19453,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -19621,13 +19621,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -19873,13 +19873,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -20293,13 +20293,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -20797,13 +20797,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
@@ -20839,13 +20839,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
@@ -21007,13 +21007,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -21049,13 +21049,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -21091,13 +21091,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -21301,13 +21301,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -21637,13 +21637,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -21889,13 +21889,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -22015,13 +22015,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
@@ -22519,13 +22519,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -22771,13 +22771,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -23191,13 +23191,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -23695,13 +23695,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -24247,13 +24247,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -24961,13 +24961,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -25087,13 +25087,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -25717,13 +25717,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -25801,13 +25801,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -26641,13 +26641,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
@@ -26683,13 +26683,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
@@ -27145,13 +27145,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -27439,13 +27439,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -27859,13 +27859,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193">
@@ -28615,13 +28615,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229">
@@ -29035,13 +29035,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249">
@@ -29539,13 +29539,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
@@ -30091,13 +30091,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -30427,13 +30427,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -30805,13 +30805,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -31141,13 +31141,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -32527,13 +32527,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
@@ -33703,13 +33703,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -34879,13 +34879,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="249">
@@ -34963,13 +34963,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -35383,13 +35383,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
@@ -35620,13 +35620,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -35746,13 +35746,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -35809,13 +35809,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -36103,13 +36103,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -36271,13 +36271,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -36481,13 +36481,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -36691,13 +36691,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -36943,13 +36943,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -36964,13 +36964,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
@@ -37552,13 +37552,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -38140,13 +38140,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -38392,13 +38392,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
@@ -38413,13 +38413,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139">
@@ -38692,13 +38692,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -39049,13 +39049,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -39112,13 +39112,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -39196,13 +39196,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -39217,13 +39217,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -39301,13 +39301,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -39427,13 +39427,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -39469,13 +39469,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39637,13 +39637,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -39889,13 +39889,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -39910,13 +39910,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
@@ -39994,13 +39994,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -40141,13 +40141,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -40309,13 +40309,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -40498,13 +40498,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -40876,13 +40876,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -41086,13 +41086,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -41338,13 +41338,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138">
@@ -41359,13 +41359,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139">
@@ -41638,13 +41638,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -41995,13 +41995,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -42247,13 +42247,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -42373,13 +42373,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -42835,13 +42835,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -42856,13 +42856,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -42940,13 +42940,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -43087,13 +43087,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -43444,13 +43444,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -43822,13 +43822,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -44032,13 +44032,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -44284,13 +44284,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
@@ -44584,13 +44584,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -44941,13 +44941,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -45193,13 +45193,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -45319,13 +45319,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -45361,13 +45361,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -45529,13 +45529,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -45781,13 +45781,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -45802,13 +45802,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -46033,13 +46033,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -46390,13 +46390,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
@@ -46642,13 +46642,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -46768,13 +46768,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -46978,13 +46978,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -47230,13 +47230,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
@@ -47251,13 +47251,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139">
@@ -47383,13 +47383,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -47530,13 +47530,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -47887,13 +47887,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -48055,13 +48055,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -48265,13 +48265,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -48748,13 +48748,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
@@ -48874,13 +48874,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -48979,13 +48979,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -49336,13 +49336,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
@@ -49714,13 +49714,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -49924,13 +49924,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -50176,13 +50176,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
@@ -50197,13 +50197,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
@@ -56200,13 +56200,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -56227,13 +56227,13 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="E5" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="F5" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="G5" t="n">
         <v>1.25</v>
@@ -56254,13 +56254,13 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>322.2</v>
+        <v>311.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -56389,13 +56389,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>4.94</v>
+        <v>4.32</v>
       </c>
       <c r="E11" t="n">
-        <v>382.5</v>
+        <v>335</v>
       </c>
       <c r="F11" t="n">
-        <v>4.35</v>
+        <v>3.74</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -56470,13 +56470,13 @@
         <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="E14" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="F14" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -56551,13 +56551,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="E17" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F17" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -56578,13 +56578,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -56605,13 +56605,13 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="E19" t="n">
-        <v>1175</v>
+        <v>1075</v>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -56767,13 +56767,13 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="E25" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="F25" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -56848,13 +56848,13 @@
         <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>12.32</v>
+        <v>11.81</v>
       </c>
       <c r="E28" t="n">
-        <v>350.5</v>
+        <v>335.8</v>
       </c>
       <c r="F28" t="n">
-        <v>12.13</v>
+        <v>11.61</v>
       </c>
       <c r="G28" t="n">
         <v>0.796</v>
@@ -56929,13 +56929,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>166.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -57037,13 +57037,13 @@
         <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="E35" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="G35" t="n">
         <v>1.333</v>
@@ -57064,13 +57064,13 @@
         <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="E36" t="n">
-        <v>362.5</v>
+        <v>400</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G36" t="n">
         <v>1.333</v>
@@ -57172,13 +57172,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="E40" t="n">
-        <v>407.1</v>
+        <v>378.6</v>
       </c>
       <c r="F40" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="G40" t="n">
         <v>1.077</v>
@@ -57226,13 +57226,13 @@
         <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="E42" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F42" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -57334,13 +57334,13 @@
         <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>4.74</v>
+        <v>4.39</v>
       </c>
       <c r="E46" t="n">
-        <v>358.5</v>
+        <v>331.7</v>
       </c>
       <c r="F46" t="n">
-        <v>4.74</v>
+        <v>4.39</v>
       </c>
       <c r="G46" t="n">
         <v>0.837</v>
@@ -57388,13 +57388,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="E48" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F48" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -57577,13 +57577,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E55" t="n">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="F55" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -57604,13 +57604,13 @@
         <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3700</v>
+        <v>3100</v>
       </c>
       <c r="F56" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -57658,13 +57658,13 @@
         <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E58" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="G58" t="n">
         <v>1.667</v>
@@ -57847,13 +57847,13 @@
         <v>31</v>
       </c>
       <c r="D65" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E65" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="F65" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -57928,13 +57928,13 @@
         <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>13.03</v>
+        <v>12.55</v>
       </c>
       <c r="E68" t="n">
-        <v>328.5</v>
+        <v>316.3</v>
       </c>
       <c r="F68" t="n">
-        <v>12.65</v>
+        <v>12.16</v>
       </c>
       <c r="G68" t="n">
         <v>0.879</v>
@@ -57955,13 +57955,13 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>13.55</v>
       </c>
       <c r="E69" t="n">
-        <v>428.7</v>
+        <v>446.8</v>
       </c>
       <c r="F69" t="n">
-        <v>12.42</v>
+        <v>12.97</v>
       </c>
       <c r="G69" t="n">
         <v>0.922</v>
@@ -58063,13 +58063,13 @@
         <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="E73" t="n">
-        <v>577.8</v>
+        <v>544.4</v>
       </c>
       <c r="F73" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="G73" t="n">
         <v>1.125</v>
@@ -58090,13 +58090,13 @@
         <v>31</v>
       </c>
       <c r="D74" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="E74" t="n">
-        <v>450</v>
+        <v>433.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -58252,13 +58252,13 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="E80" t="n">
-        <v>403.4</v>
+        <v>375.9</v>
       </c>
       <c r="F80" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="G80" t="n">
         <v>0.829</v>
@@ -58414,13 +58414,13 @@
         <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E86" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F86" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -58441,13 +58441,13 @@
         <v>31</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E87" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F87" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -58468,13 +58468,13 @@
         <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="E88" t="n">
-        <v>361.5</v>
+        <v>338.5</v>
       </c>
       <c r="F88" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="G88" t="n">
         <v>1.857</v>
@@ -58630,13 +58630,13 @@
         <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="E94" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="F94" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -58711,13 +58711,13 @@
         <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>10.94</v>
+        <v>10.61</v>
       </c>
       <c r="E97" t="n">
-        <v>360.6</v>
+        <v>350</v>
       </c>
       <c r="F97" t="n">
-        <v>10.94</v>
+        <v>10.61</v>
       </c>
       <c r="G97" t="n">
         <v>0.847</v>
@@ -58792,13 +58792,13 @@
         <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="E100" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="F100" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -59035,13 +59035,13 @@
         <v>31</v>
       </c>
       <c r="D109" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="E109" t="n">
-        <v>437.5</v>
+        <v>400</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G109" t="n">
         <v>1.333</v>
@@ -59197,13 +59197,13 @@
         <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="E115" t="n">
-        <v>389.3</v>
+        <v>360.7</v>
       </c>
       <c r="F115" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="G115" t="n">
         <v>0.778</v>
@@ -59467,13 +59467,13 @@
         <v>31</v>
       </c>
       <c r="D125" t="n">
-        <v>5.03</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>1040</v>
+        <v>826.7</v>
       </c>
       <c r="F125" t="n">
-        <v>4.58</v>
+        <v>3.55</v>
       </c>
       <c r="G125" t="n">
         <v>1.875</v>
@@ -59521,13 +59521,13 @@
         <v>31</v>
       </c>
       <c r="D127" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="E127" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="F127" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -59791,13 +59791,13 @@
         <v>31</v>
       </c>
       <c r="D137" t="n">
-        <v>11.35</v>
+        <v>10.94</v>
       </c>
       <c r="E137" t="n">
-        <v>362.9</v>
+        <v>349.5</v>
       </c>
       <c r="F137" t="n">
-        <v>11.35</v>
+        <v>10.94</v>
       </c>
       <c r="G137" t="n">
         <v>0.851</v>
@@ -59818,13 +59818,13 @@
         <v>31</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39</v>
+        <v>17.26</v>
       </c>
       <c r="E138" t="n">
-        <v>343.3</v>
+        <v>340.8</v>
       </c>
       <c r="F138" t="n">
-        <v>16.74</v>
+        <v>16.61</v>
       </c>
       <c r="G138" t="n">
         <v>0.9350000000000001</v>
@@ -71737,13 +71737,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -73501,13 +73501,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -73585,13 +73585,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -76819,13 +76819,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -78211,13 +78211,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -78589,13 +78589,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -79345,13 +79345,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -80311,13 +80311,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
@@ -80773,13 +80773,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -82663,13 +82663,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -86113,13 +86113,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
@@ -86155,13 +86155,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
@@ -86617,13 +86617,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -87331,13 +87331,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193">
@@ -88087,13 +88087,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229">
@@ -88507,13 +88507,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -89899,13 +89899,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -90277,13 +90277,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -90865,13 +90865,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -91117,13 +91117,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -91411,13 +91411,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -91453,13 +91453,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -91957,13 +91957,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
@@ -91999,13 +91999,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
@@ -93301,13 +93301,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -94351,13 +94351,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -94813,13 +94813,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -94897,13 +94897,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="275">

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -27,6 +27,7 @@
     <sheet name="04-06" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="04-07" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Accuracy Summary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Confidence" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59862,6 +59863,4908 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Data Points</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg MAE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Demand</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Demand CV</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Correction Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>31</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>31</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>31</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>31</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>31</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>31</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>31</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>31</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>31</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>31</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>31</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>31</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>31</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>31</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>31</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>31</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>31</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>31</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>31</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>31</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>65</v>
+      </c>
+      <c r="E57" t="n">
+        <v>31</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>65</v>
+      </c>
+      <c r="E58" t="n">
+        <v>31</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>65</v>
+      </c>
+      <c r="E59" t="n">
+        <v>31</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>65</v>
+      </c>
+      <c r="E60" t="n">
+        <v>31</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>65</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>65</v>
+      </c>
+      <c r="E62" t="n">
+        <v>31</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>65</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>65</v>
+      </c>
+      <c r="E64" t="n">
+        <v>31</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>65</v>
+      </c>
+      <c r="E65" t="n">
+        <v>31</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>65</v>
+      </c>
+      <c r="E66" t="n">
+        <v>31</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>65</v>
+      </c>
+      <c r="E67" t="n">
+        <v>31</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>65</v>
+      </c>
+      <c r="E68" t="n">
+        <v>31</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>65</v>
+      </c>
+      <c r="E69" t="n">
+        <v>31</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>65</v>
+      </c>
+      <c r="E70" t="n">
+        <v>31</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>65</v>
+      </c>
+      <c r="E71" t="n">
+        <v>31</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>31</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>31</v>
+      </c>
+      <c r="F73" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>31</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>31</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>31</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.851</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>31</v>
+      </c>
+      <c r="F77" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>31</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.829</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>31</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.837</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>31</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>45</v>
+      </c>
+      <c r="E81" t="n">
+        <v>31</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>45</v>
+      </c>
+      <c r="E82" t="n">
+        <v>31</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>45</v>
+      </c>
+      <c r="E83" t="n">
+        <v>31</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>45</v>
+      </c>
+      <c r="E84" t="n">
+        <v>31</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H84" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>45</v>
+      </c>
+      <c r="E85" t="n">
+        <v>31</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>45</v>
+      </c>
+      <c r="E86" t="n">
+        <v>31</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>45</v>
+      </c>
+      <c r="E87" t="n">
+        <v>31</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>45</v>
+      </c>
+      <c r="E88" t="n">
+        <v>31</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>45</v>
+      </c>
+      <c r="E89" t="n">
+        <v>31</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>45</v>
+      </c>
+      <c r="E90" t="n">
+        <v>31</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>45</v>
+      </c>
+      <c r="E91" t="n">
+        <v>31</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>45</v>
+      </c>
+      <c r="E92" t="n">
+        <v>31</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>45</v>
+      </c>
+      <c r="E93" t="n">
+        <v>31</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>45</v>
+      </c>
+      <c r="E94" t="n">
+        <v>31</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>45</v>
+      </c>
+      <c r="E95" t="n">
+        <v>31</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H95" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>45</v>
+      </c>
+      <c r="E96" t="n">
+        <v>31</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>45</v>
+      </c>
+      <c r="E97" t="n">
+        <v>31</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>45</v>
+      </c>
+      <c r="E98" t="n">
+        <v>31</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>45</v>
+      </c>
+      <c r="E99" t="n">
+        <v>31</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>45</v>
+      </c>
+      <c r="E100" t="n">
+        <v>31</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>45</v>
+      </c>
+      <c r="E101" t="n">
+        <v>31</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>45</v>
+      </c>
+      <c r="E102" t="n">
+        <v>31</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>45</v>
+      </c>
+      <c r="E103" t="n">
+        <v>31</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>45</v>
+      </c>
+      <c r="E104" t="n">
+        <v>31</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>45</v>
+      </c>
+      <c r="E105" t="n">
+        <v>31</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>45</v>
+      </c>
+      <c r="E106" t="n">
+        <v>31</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>45</v>
+      </c>
+      <c r="E107" t="n">
+        <v>31</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>45</v>
+      </c>
+      <c r="E108" t="n">
+        <v>31</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>45</v>
+      </c>
+      <c r="E109" t="n">
+        <v>31</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>45</v>
+      </c>
+      <c r="E110" t="n">
+        <v>31</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>45</v>
+      </c>
+      <c r="E111" t="n">
+        <v>31</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>45</v>
+      </c>
+      <c r="E112" t="n">
+        <v>31</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>45</v>
+      </c>
+      <c r="E113" t="n">
+        <v>31</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>45</v>
+      </c>
+      <c r="E114" t="n">
+        <v>31</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>45</v>
+      </c>
+      <c r="E115" t="n">
+        <v>31</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>45</v>
+      </c>
+      <c r="E116" t="n">
+        <v>31</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>45</v>
+      </c>
+      <c r="E117" t="n">
+        <v>31</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>45</v>
+      </c>
+      <c r="E118" t="n">
+        <v>31</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>45</v>
+      </c>
+      <c r="E119" t="n">
+        <v>31</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>45</v>
+      </c>
+      <c r="E120" t="n">
+        <v>31</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H120" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>45</v>
+      </c>
+      <c r="E121" t="n">
+        <v>31</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>45</v>
+      </c>
+      <c r="E122" t="n">
+        <v>31</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>45</v>
+      </c>
+      <c r="E123" t="n">
+        <v>31</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>45</v>
+      </c>
+      <c r="E124" t="n">
+        <v>31</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>31</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.778</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>31</v>
+      </c>
+      <c r="F126" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E127" t="n">
+        <v>31</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.077</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>31</v>
+      </c>
+      <c r="F128" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.796</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>31</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>43</v>
+      </c>
+      <c r="E130" t="n">
+        <v>31</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>42</v>
+      </c>
+      <c r="E131" t="n">
+        <v>31</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H131" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>42</v>
+      </c>
+      <c r="E132" t="n">
+        <v>31</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1.222</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>40</v>
+      </c>
+      <c r="E133" t="n">
+        <v>31</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>40</v>
+      </c>
+      <c r="E134" t="n">
+        <v>31</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>40</v>
+      </c>
+      <c r="E135" t="n">
+        <v>31</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>35</v>
+      </c>
+      <c r="E136" t="n">
+        <v>31</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.667</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>31</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.857</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E138" t="n">
+        <v>31</v>
+      </c>
+      <c r="F138" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>30</v>
+      </c>
+      <c r="E139" t="n">
+        <v>31</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -56201,16 +56201,16 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="E4" t="n">
-        <v>3400</v>
+        <v>1066.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -56228,16 +56228,16 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="E5" t="n">
-        <v>420</v>
+        <v>271.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="6">
@@ -56255,16 +56255,16 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="E6" t="n">
-        <v>311.1</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="7">
@@ -56309,13 +56309,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="E8" t="n">
-        <v>1450</v>
+        <v>675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -56363,13 +56363,13 @@
         <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -56390,13 +56390,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>4.32</v>
+        <v>4.06</v>
       </c>
       <c r="E11" t="n">
-        <v>335</v>
+        <v>262.5</v>
       </c>
       <c r="F11" t="n">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -56444,13 +56444,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -56633,13 +56633,13 @@
         <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="E20" t="n">
-        <v>416.7</v>
+        <v>287.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -56741,13 +56741,13 @@
         <v>31</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>1450</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -56849,16 +56849,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>11.81</v>
+        <v>11.16</v>
       </c>
       <c r="E28" t="n">
-        <v>335.8</v>
+        <v>268.2</v>
       </c>
       <c r="F28" t="n">
-        <v>11.61</v>
+        <v>10.97</v>
       </c>
       <c r="G28" t="n">
-        <v>0.796</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="29">
@@ -56984,13 +56984,13 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -57065,16 +57065,16 @@
         <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="E36" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="G36" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="37">
@@ -57119,13 +57119,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -57176,13 +57176,13 @@
         <v>1.71</v>
       </c>
       <c r="E40" t="n">
-        <v>378.6</v>
+        <v>240.9</v>
       </c>
       <c r="F40" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="G40" t="n">
-        <v>1.077</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="41">
@@ -57335,16 +57335,16 @@
         <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>4.39</v>
+        <v>4.19</v>
       </c>
       <c r="E46" t="n">
-        <v>331.7</v>
+        <v>254.9</v>
       </c>
       <c r="F46" t="n">
-        <v>4.39</v>
+        <v>4.06</v>
       </c>
       <c r="G46" t="n">
-        <v>0.837</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="47">
@@ -57362,13 +57362,13 @@
         <v>31</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -57443,13 +57443,13 @@
         <v>31</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="E50" t="n">
-        <v>1450</v>
+        <v>675</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -57578,13 +57578,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="E55" t="n">
-        <v>325</v>
+        <v>212.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -57659,16 +57659,16 @@
         <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="E58" t="n">
-        <v>560</v>
+        <v>371.4</v>
       </c>
       <c r="F58" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="G58" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="59">
@@ -57875,13 +57875,13 @@
         <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="E66" t="n">
-        <v>125</v>
+        <v>116.7</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -57929,16 +57929,16 @@
         <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>12.55</v>
+        <v>11.65</v>
       </c>
       <c r="E68" t="n">
-        <v>316.3</v>
+        <v>235.9</v>
       </c>
       <c r="F68" t="n">
-        <v>12.16</v>
+        <v>11.19</v>
       </c>
       <c r="G68" t="n">
-        <v>0.879</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="69">
@@ -57956,16 +57956,16 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="E69" t="n">
-        <v>446.8</v>
+        <v>275.7</v>
       </c>
       <c r="F69" t="n">
-        <v>12.97</v>
+        <v>11.23</v>
       </c>
       <c r="G69" t="n">
-        <v>0.922</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="70">
@@ -58064,16 +58064,16 @@
         <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="E73" t="n">
-        <v>544.4</v>
+        <v>427.3</v>
       </c>
       <c r="F73" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="G73" t="n">
-        <v>1.125</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="74">
@@ -58253,16 +58253,16 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="E80" t="n">
-        <v>375.9</v>
+        <v>294.3</v>
       </c>
       <c r="F80" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="G80" t="n">
-        <v>0.829</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="81">
@@ -58415,13 +58415,13 @@
         <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="E86" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="F86" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -58604,13 +58604,13 @@
         <v>31</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E93" t="n">
-        <v>3100</v>
+        <v>1450</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -58712,16 +58712,16 @@
         <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>10.61</v>
+        <v>9.9</v>
       </c>
       <c r="E97" t="n">
-        <v>350</v>
+        <v>264.7</v>
       </c>
       <c r="F97" t="n">
-        <v>10.61</v>
+        <v>9.9</v>
       </c>
       <c r="G97" t="n">
-        <v>0.847</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="98">
@@ -58847,13 +58847,13 @@
         <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="E102" t="n">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -58928,13 +58928,13 @@
         <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="E105" t="n">
-        <v>520</v>
+        <v>342.9</v>
       </c>
       <c r="F105" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -58982,13 +58982,13 @@
         <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -59036,16 +59036,16 @@
         <v>31</v>
       </c>
       <c r="D109" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="E109" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="G109" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="110">
@@ -59066,13 +59066,13 @@
         <v>0.32</v>
       </c>
       <c r="E110" t="n">
-        <v>500</v>
+        <v>166.7</v>
       </c>
       <c r="F110" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -59198,16 +59198,16 @@
         <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>3.26</v>
+        <v>3.06</v>
       </c>
       <c r="E115" t="n">
-        <v>360.7</v>
+        <v>263.9</v>
       </c>
       <c r="F115" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>0.778</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="116">
@@ -59390,10 +59390,10 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>3100</v>
+        <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -59468,16 +59468,16 @@
         <v>31</v>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="E125" t="n">
-        <v>826.7</v>
+        <v>464</v>
       </c>
       <c r="F125" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="G125" t="n">
-        <v>1.875</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="126">
@@ -59792,16 +59792,16 @@
         <v>31</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94</v>
+        <v>10.23</v>
       </c>
       <c r="E137" t="n">
-        <v>349.5</v>
+        <v>266.4</v>
       </c>
       <c r="F137" t="n">
-        <v>10.94</v>
+        <v>10.23</v>
       </c>
       <c r="G137" t="n">
-        <v>0.851</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="138">
@@ -59819,16 +59819,16 @@
         <v>31</v>
       </c>
       <c r="D138" t="n">
-        <v>17.26</v>
+        <v>16.03</v>
       </c>
       <c r="E138" t="n">
-        <v>340.8</v>
+        <v>249.7</v>
       </c>
       <c r="F138" t="n">
-        <v>16.61</v>
+        <v>15.26</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="139">
@@ -59973,7 +59973,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -60008,7 +60008,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -60043,7 +60043,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -60078,7 +60078,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -60113,7 +60113,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -60148,7 +60148,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -60183,7 +60183,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -60213,12 +60213,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -60283,12 +60283,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -60323,7 +60323,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -60358,7 +60358,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -60393,7 +60393,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -60428,7 +60428,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -60463,7 +60463,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -60498,7 +60498,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -60533,7 +60533,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -60563,12 +60563,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -60603,7 +60603,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -60633,12 +60633,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -60673,7 +60673,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -60708,7 +60708,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -60743,7 +60743,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -60778,7 +60778,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -60813,7 +60813,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -60848,7 +60848,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -60883,7 +60883,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -60918,7 +60918,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -60953,7 +60953,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -60988,7 +60988,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -61058,7 +61058,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -61093,7 +61093,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -61128,7 +61128,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -61163,7 +61163,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -61198,7 +61198,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -61233,7 +61233,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -61263,12 +61263,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -61298,12 +61298,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -61333,12 +61333,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -61373,7 +61373,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -61408,7 +61408,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -61443,7 +61443,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -61478,7 +61478,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -61513,7 +61513,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -61548,7 +61548,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -61583,7 +61583,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -61618,7 +61618,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -61653,7 +61653,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -61688,7 +61688,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -61723,7 +61723,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -61758,22 +61758,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>82.5</v>
+        <v>65</v>
       </c>
       <c r="E54" t="n">
         <v>31</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -61788,27 +61788,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>82.5</v>
+        <v>65</v>
       </c>
       <c r="E55" t="n">
         <v>31</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -61828,22 +61828,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>82.5</v>
+        <v>65</v>
       </c>
       <c r="E56" t="n">
         <v>31</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -61858,12 +61858,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -61878,7 +61878,7 @@
         <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -61898,7 +61898,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -61913,7 +61913,7 @@
         <v>31</v>
       </c>
       <c r="F58" t="n">
-        <v>0.19</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -61933,7 +61933,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -61948,7 +61948,7 @@
         <v>31</v>
       </c>
       <c r="F59" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -61998,12 +61998,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -62018,7 +62018,7 @@
         <v>31</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -62038,7 +62038,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -62053,7 +62053,7 @@
         <v>31</v>
       </c>
       <c r="F62" t="n">
-        <v>0.55</v>
+        <v>0.03</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -62073,7 +62073,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -62088,7 +62088,7 @@
         <v>31</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -62103,12 +62103,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -62138,12 +62138,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -62152,33 +62152,33 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>49.6</v>
       </c>
       <c r="E65" t="n">
         <v>31</v>
       </c>
       <c r="F65" t="n">
-        <v>0.16</v>
+        <v>16.03</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Buttercream</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -62187,19 +62187,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>49.5</v>
       </c>
       <c r="E66" t="n">
         <v>31</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>4.06</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -62208,12 +62208,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Vienna Cream</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -62222,22 +62222,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E67" t="n">
         <v>31</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>11.65</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="68">
@@ -62248,7 +62248,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>Oat Milk</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -62257,22 +62257,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>65</v>
+        <v>48.7</v>
       </c>
       <c r="E68" t="n">
         <v>31</v>
       </c>
       <c r="F68" t="n">
-        <v>0.03</v>
+        <v>4.19</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="69">
@@ -62283,7 +62283,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -62292,19 +62292,19 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
         <v>31</v>
       </c>
       <c r="F69" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -62318,7 +62318,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>Vienna Cream</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -62327,33 +62327,33 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E70" t="n">
         <v>31</v>
       </c>
       <c r="F70" t="n">
-        <v>0.13</v>
+        <v>10.23</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Oat Milk</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -62362,33 +62362,33 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>65</v>
+        <v>47.9</v>
       </c>
       <c r="E71" t="n">
         <v>31</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3.06</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Buttercream</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -62397,22 +62397,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="E72" t="n">
         <v>31</v>
       </c>
       <c r="F72" t="n">
-        <v>4.32</v>
+        <v>9.9</v>
       </c>
       <c r="G72" t="n">
-        <v>1.29</v>
+        <v>3.74</v>
       </c>
       <c r="H72" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="73">
@@ -62423,7 +62423,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
+          <t>Buttercream</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -62432,33 +62432,33 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>46.8</v>
+        <v>47.2</v>
       </c>
       <c r="E73" t="n">
         <v>31</v>
       </c>
       <c r="F73" t="n">
-        <v>17.26</v>
+        <v>3.32</v>
       </c>
       <c r="G73" t="n">
-        <v>5.06</v>
+        <v>1.13</v>
       </c>
       <c r="H73" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -62467,33 +62467,33 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="E74" t="n">
         <v>31</v>
       </c>
       <c r="F74" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="G74" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="H74" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vienna Cream</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -62502,22 +62502,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="E75" t="n">
         <v>31</v>
       </c>
       <c r="F75" t="n">
-        <v>12.55</v>
+        <v>0.77</v>
       </c>
       <c r="G75" t="n">
-        <v>3.97</v>
+        <v>0.23</v>
       </c>
       <c r="H75" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="I75" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -62528,7 +62528,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vienna Cream</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -62537,28 +62537,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>45.7</v>
+        <v>46.5</v>
       </c>
       <c r="E76" t="n">
         <v>31</v>
       </c>
       <c r="F76" t="n">
-        <v>10.94</v>
+        <v>0.77</v>
       </c>
       <c r="G76" t="n">
-        <v>3.13</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="I76" t="n">
-        <v>0.851</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -62572,22 +62572,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="E77" t="n">
         <v>31</v>
       </c>
       <c r="F77" t="n">
-        <v>10.61</v>
+        <v>11.16</v>
       </c>
       <c r="G77" t="n">
-        <v>3.03</v>
+        <v>4.16</v>
       </c>
       <c r="H77" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="I77" t="n">
-        <v>0.847</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="78">
@@ -62598,7 +62598,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Buttercream</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -62607,33 +62607,33 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>45.3</v>
+        <v>45</v>
       </c>
       <c r="E78" t="n">
         <v>31</v>
       </c>
       <c r="F78" t="n">
-        <v>3.52</v>
+        <v>0.19</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="H78" t="n">
-        <v>1.72</v>
+        <v>3.81</v>
       </c>
       <c r="I78" t="n">
-        <v>0.829</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Oat Milk</t>
+          <t>Mocha</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -62642,33 +62642,33 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="E79" t="n">
         <v>31</v>
       </c>
       <c r="F79" t="n">
-        <v>4.39</v>
+        <v>0.06</v>
       </c>
       <c r="G79" t="n">
-        <v>1.32</v>
+        <v>0.06</v>
       </c>
       <c r="H79" t="n">
-        <v>1.73</v>
+        <v>3.81</v>
       </c>
       <c r="I79" t="n">
-        <v>0.837</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Almond Milk</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -62677,19 +62677,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="E80" t="n">
         <v>31</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="G80" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="H80" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -62703,7 +62703,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -62718,13 +62718,13 @@
         <v>31</v>
       </c>
       <c r="F81" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="G81" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H81" t="n">
-        <v>3.81</v>
+        <v>2.6</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -62733,12 +62733,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -62753,13 +62753,13 @@
         <v>31</v>
       </c>
       <c r="F82" t="n">
-        <v>0.84</v>
+        <v>0.16</v>
       </c>
       <c r="G82" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="H82" t="n">
-        <v>2.28</v>
+        <v>5.48</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -62768,12 +62768,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -62788,13 +62788,13 @@
         <v>31</v>
       </c>
       <c r="F83" t="n">
-        <v>0.16</v>
+        <v>0.87</v>
       </c>
       <c r="G83" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H83" t="n">
-        <v>3.81</v>
+        <v>2.6</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -62803,12 +62803,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -62823,13 +62823,13 @@
         <v>31</v>
       </c>
       <c r="F84" t="n">
-        <v>1.39</v>
+        <v>0.06</v>
       </c>
       <c r="G84" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H84" t="n">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -62843,7 +62843,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Paper Bag</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -62878,7 +62878,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -62893,10 +62893,10 @@
         <v>31</v>
       </c>
       <c r="F86" t="n">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>0.06</v>
+        <v>0.65</v>
       </c>
       <c r="H86" t="n">
         <v>3.81</v>
@@ -62908,12 +62908,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -62928,13 +62928,13 @@
         <v>31</v>
       </c>
       <c r="F87" t="n">
-        <v>0.48</v>
+        <v>0.06</v>
       </c>
       <c r="G87" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H87" t="n">
-        <v>2.6</v>
+        <v>3.81</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -62943,12 +62943,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -62963,13 +62963,13 @@
         <v>31</v>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>0.13</v>
       </c>
       <c r="G88" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>3.81</v>
+        <v>2.6</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -62978,12 +62978,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -62998,13 +62998,13 @@
         <v>31</v>
       </c>
       <c r="F89" t="n">
-        <v>1.1</v>
+        <v>0.52</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="H89" t="n">
-        <v>5.48</v>
+        <v>2.28</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -63048,12 +63048,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -63068,13 +63068,13 @@
         <v>31</v>
       </c>
       <c r="F91" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H91" t="n">
-        <v>3.06</v>
+        <v>3.81</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -63088,7 +63088,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -63103,7 +63103,7 @@
         <v>31</v>
       </c>
       <c r="F92" t="n">
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="G92" t="n">
         <v>0.06</v>
@@ -63118,12 +63118,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -63138,13 +63138,13 @@
         <v>31</v>
       </c>
       <c r="F93" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="G93" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H93" t="n">
-        <v>3.81</v>
+        <v>2.28</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -63153,12 +63153,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -63173,13 +63173,13 @@
         <v>31</v>
       </c>
       <c r="F94" t="n">
-        <v>0.52</v>
+        <v>0.1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H94" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mocha</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -63208,10 +63208,10 @@
         <v>31</v>
       </c>
       <c r="F95" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H95" t="n">
         <v>3.81</v>
@@ -63228,7 +63228,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -63243,13 +63243,13 @@
         <v>31</v>
       </c>
       <c r="F96" t="n">
-        <v>0.06</v>
+        <v>0.87</v>
       </c>
       <c r="G96" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H96" t="n">
-        <v>3.81</v>
+        <v>2.6</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -63263,7 +63263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -63278,7 +63278,7 @@
         <v>31</v>
       </c>
       <c r="F97" t="n">
-        <v>0.68</v>
+        <v>0.19</v>
       </c>
       <c r="G97" t="n">
         <v>0.06</v>
@@ -63328,12 +63328,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -63348,13 +63348,13 @@
         <v>31</v>
       </c>
       <c r="F99" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G99" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="H99" t="n">
-        <v>5.48</v>
+        <v>2.6</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -63363,12 +63363,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mocha</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -63383,13 +63383,13 @@
         <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>0.35</v>
+        <v>0.03</v>
       </c>
       <c r="G100" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="H100" t="n">
-        <v>3.81</v>
+        <v>5.48</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -63403,7 +63403,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -63418,13 +63418,13 @@
         <v>31</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="G101" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H101" t="n">
-        <v>2.04</v>
+        <v>5.48</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -63438,7 +63438,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -63453,13 +63453,13 @@
         <v>31</v>
       </c>
       <c r="F102" t="n">
-        <v>0.84</v>
+        <v>0.39</v>
       </c>
       <c r="G102" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="H102" t="n">
-        <v>2.04</v>
+        <v>3.81</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -63473,7 +63473,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -63488,13 +63488,13 @@
         <v>31</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H103" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -63508,7 +63508,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Paper Bag</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -63523,13 +63523,13 @@
         <v>31</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="G104" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="H104" t="n">
-        <v>3.81</v>
+        <v>2.04</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -63543,7 +63543,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -63558,13 +63558,13 @@
         <v>31</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="G105" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H105" t="n">
-        <v>3.81</v>
+        <v>3.06</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -63578,7 +63578,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -63593,13 +63593,13 @@
         <v>31</v>
       </c>
       <c r="F106" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G106" t="n">
         <v>0.06</v>
       </c>
       <c r="H106" t="n">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -63608,12 +63608,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -63628,13 +63628,13 @@
         <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="G107" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>3.81</v>
+        <v>2.04</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -63643,12 +63643,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -63663,13 +63663,13 @@
         <v>31</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H108" t="n">
-        <v>3.06</v>
+        <v>3.81</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -63678,12 +63678,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -63698,13 +63698,13 @@
         <v>31</v>
       </c>
       <c r="F109" t="n">
-        <v>0.42</v>
+        <v>0.03</v>
       </c>
       <c r="G109" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="H109" t="n">
-        <v>3.81</v>
+        <v>5.48</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -63713,12 +63713,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -63748,12 +63748,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -63768,13 +63768,13 @@
         <v>31</v>
       </c>
       <c r="F111" t="n">
-        <v>0.45</v>
+        <v>0.06</v>
       </c>
       <c r="G111" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H111" t="n">
-        <v>2.6</v>
+        <v>3.81</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -63788,7 +63788,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -63803,10 +63803,10 @@
         <v>31</v>
       </c>
       <c r="F112" t="n">
-        <v>0.16</v>
+        <v>0.55</v>
       </c>
       <c r="G112" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H112" t="n">
         <v>2.6</v>
@@ -63818,12 +63818,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -63838,13 +63838,13 @@
         <v>31</v>
       </c>
       <c r="F113" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G113" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>3.81</v>
+        <v>3.06</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -63853,12 +63853,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -63893,7 +63893,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -63908,10 +63908,10 @@
         <v>31</v>
       </c>
       <c r="F115" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H115" t="n">
         <v>3.06</v>
@@ -63928,7 +63928,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -63946,10 +63946,10 @@
         <v>0.06</v>
       </c>
       <c r="G116" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H116" t="n">
-        <v>3.81</v>
+        <v>5.48</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -63958,12 +63958,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -63978,7 +63978,7 @@
         <v>31</v>
       </c>
       <c r="F117" t="n">
-        <v>0.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G117" t="n">
         <v>0.06</v>
@@ -63993,12 +63993,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -64013,7 +64013,7 @@
         <v>31</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="G118" t="n">
         <v>0.06</v>
@@ -64028,12 +64028,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -64048,13 +64048,13 @@
         <v>31</v>
       </c>
       <c r="F119" t="n">
-        <v>0.06</v>
+        <v>0.58</v>
       </c>
       <c r="G119" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H119" t="n">
-        <v>3.81</v>
+        <v>2.6</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -64068,7 +64068,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -64083,13 +64083,13 @@
         <v>31</v>
       </c>
       <c r="F120" t="n">
-        <v>0.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H120" t="n">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -64103,7 +64103,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Mocha</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -64118,13 +64118,13 @@
         <v>31</v>
       </c>
       <c r="F121" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="G121" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H121" t="n">
-        <v>3.06</v>
+        <v>3.81</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -64133,12 +64133,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -64153,13 +64153,13 @@
         <v>31</v>
       </c>
       <c r="F122" t="n">
-        <v>0.58</v>
+        <v>0.06</v>
       </c>
       <c r="G122" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H122" t="n">
-        <v>2.6</v>
+        <v>3.81</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -64173,7 +64173,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -64191,10 +64191,10 @@
         <v>0.06</v>
       </c>
       <c r="G123" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H123" t="n">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -64203,12 +64203,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -64223,10 +64223,10 @@
         <v>31</v>
       </c>
       <c r="F124" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H124" t="n">
         <v>3.81</v>
@@ -64243,7 +64243,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Oat Milk</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -64252,22 +64252,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="E125" t="n">
         <v>31</v>
       </c>
       <c r="F125" t="n">
-        <v>3.26</v>
+        <v>1.52</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="H125" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="I125" t="n">
-        <v>0.778</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="126">
@@ -64287,22 +64287,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="E126" t="n">
         <v>31</v>
       </c>
       <c r="F126" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="G126" t="n">
-        <v>3.03</v>
+        <v>4.77</v>
       </c>
       <c r="H126" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="I126" t="n">
-        <v>0.922</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="127">
@@ -64322,7 +64322,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>43.8</v>
+        <v>43</v>
       </c>
       <c r="E127" t="n">
         <v>31</v>
@@ -64331,24 +64331,24 @@
         <v>1.71</v>
       </c>
       <c r="G127" t="n">
-        <v>0.45</v>
+        <v>0.71</v>
       </c>
       <c r="H127" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="I127" t="n">
-        <v>1.077</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -64357,33 +64357,33 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="E128" t="n">
         <v>31</v>
       </c>
       <c r="F128" t="n">
-        <v>11.81</v>
+        <v>0.97</v>
       </c>
       <c r="G128" t="n">
-        <v>3.52</v>
+        <v>0.32</v>
       </c>
       <c r="H128" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I128" t="n">
-        <v>0.796</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -64392,33 +64392,33 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="E129" t="n">
         <v>31</v>
       </c>
       <c r="F129" t="n">
-        <v>1.58</v>
+        <v>0.97</v>
       </c>
       <c r="G129" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H129" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="I129" t="n">
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -64427,22 +64427,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E130" t="n">
         <v>31</v>
       </c>
       <c r="F130" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="G130" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H130" t="n">
-        <v>1.83</v>
+        <v>3.06</v>
       </c>
       <c r="I130" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="131">
@@ -64453,7 +64453,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Almond Milk</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -64468,22 +64468,22 @@
         <v>31</v>
       </c>
       <c r="F131" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="G131" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H131" t="n">
-        <v>3.06</v>
+        <v>1.97</v>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -64497,33 +64497,33 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="E132" t="n">
         <v>31</v>
       </c>
       <c r="F132" t="n">
-        <v>1.45</v>
+        <v>0.97</v>
       </c>
       <c r="G132" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="H132" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="I132" t="n">
-        <v>1.222</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -64538,7 +64538,7 @@
         <v>31</v>
       </c>
       <c r="F133" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="G133" t="n">
         <v>0.26</v>
@@ -64558,31 +64558,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E134" t="n">
         <v>31</v>
       </c>
       <c r="F134" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="G134" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H134" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="I134" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="135">
@@ -64593,42 +64593,42 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E135" t="n">
         <v>31</v>
       </c>
       <c r="F135" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="G135" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="H135" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="I135" t="n">
-        <v>1.333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -64637,22 +64637,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>35</v>
+        <v>37.9</v>
       </c>
       <c r="E136" t="n">
         <v>31</v>
       </c>
       <c r="F136" t="n">
-        <v>0.9</v>
+        <v>3.74</v>
       </c>
       <c r="G136" t="n">
-        <v>0.16</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H136" t="n">
-        <v>3.19</v>
+        <v>2.28</v>
       </c>
       <c r="I136" t="n">
-        <v>1.667</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="137">
@@ -64693,12 +64693,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -64707,33 +64707,33 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>31.9</v>
+        <v>30</v>
       </c>
       <c r="E138" t="n">
         <v>31</v>
       </c>
       <c r="F138" t="n">
-        <v>4</v>
+        <v>0.61</v>
       </c>
       <c r="G138" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="H138" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="I138" t="n">
-        <v>1.875</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -64748,13 +64748,13 @@
         <v>31</v>
       </c>
       <c r="F139" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="G139" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="I139" t="n">
         <v>2</v>
@@ -76643,10 +76643,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -76664,10 +76664,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -76685,10 +76685,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -76706,10 +76706,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -76727,10 +76727,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -76748,10 +76748,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -76811,10 +76811,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -76832,10 +76832,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -76895,10 +76895,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -76916,10 +76916,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -76937,10 +76937,10 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -76958,10 +76958,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -77021,10 +77021,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -77042,10 +77042,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -77315,10 +77315,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -77336,10 +77336,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -77483,10 +77483,10 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -77504,10 +77504,10 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -77651,10 +77651,10 @@
         <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -77672,10 +77672,10 @@
         <v>16</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -77861,10 +77861,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -77882,10 +77882,10 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -77987,10 +77987,10 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -78008,10 +78008,10 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -78071,10 +78071,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -78092,10 +78092,10 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -78155,7 +78155,7 @@
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -78176,7 +78176,7 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -78407,10 +78407,10 @@
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -78428,10 +78428,10 @@
         <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -78449,10 +78449,10 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -78470,10 +78470,10 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -78575,10 +78575,10 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -78596,10 +78596,10 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -78785,10 +78785,10 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -78806,10 +78806,10 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -78911,10 +78911,10 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -78932,10 +78932,10 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -79247,10 +79247,10 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -79268,10 +79268,10 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -79331,10 +79331,10 @@
         <v>14</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E134" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -79352,10 +79352,10 @@
         <v>15</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E135" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -79373,10 +79373,10 @@
         <v>16</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E136" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
@@ -79394,10 +79394,10 @@
         <v>17</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E137" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
@@ -79541,10 +79541,10 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -79562,10 +79562,10 @@
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -79835,10 +79835,10 @@
         <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -79856,10 +79856,10 @@
         <v>5</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -80087,10 +80087,10 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -80108,10 +80108,10 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -80381,10 +80381,10 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -80402,10 +80402,10 @@
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -80549,10 +80549,10 @@
         <v>13</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E192" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
@@ -80570,10 +80570,10 @@
         <v>16</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E193" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -80759,10 +80759,10 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -80780,10 +80780,10 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -80885,10 +80885,10 @@
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -80906,10 +80906,10 @@
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -80969,10 +80969,10 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -80990,10 +80990,10 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -81053,10 +81053,10 @@
         <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -81074,10 +81074,10 @@
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -81095,7 +81095,7 @@
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -81116,7 +81116,7 @@
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E219" t="n">
         <v>1</v>
@@ -81305,10 +81305,10 @@
         <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -81326,10 +81326,10 @@
         <v>4</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E229" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -81599,7 +81599,7 @@
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
@@ -81620,7 +81620,7 @@
         <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E243" t="n">
         <v>1</v>
@@ -81725,10 +81725,10 @@
         <v>5</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E248" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -81746,10 +81746,10 @@
         <v>4</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E249" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -82229,10 +82229,10 @@
         <v>13</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E272" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -82250,10 +82250,10 @@
         <v>15</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E273" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274">
@@ -82271,10 +82271,10 @@
         <v>19</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E274" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -82292,10 +82292,10 @@
         <v>21</v>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E275" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -17,8 +17,9 @@
     <sheet name="03-27" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="03-28" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="03-29" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Accuracy Summary" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Confidence" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="03-30" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Accuracy Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Confidence" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6328,15 +6329,2961 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>20</v>
+      </c>
+      <c r="D68" t="n">
+        <v>13</v>
+      </c>
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="n">
+        <v>9</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>11</v>
+      </c>
+      <c r="D137" t="n">
+        <v>9</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>20</v>
+      </c>
+      <c r="D138" t="n">
+        <v>18</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6389,7 +9336,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -6416,16 +9363,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -6443,16 +9390,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="G4" t="n">
         <v>1.667</v>
@@ -6470,16 +9417,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="E5" t="n">
-        <v>38.5</v>
+        <v>53.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="G5" t="n">
         <v>1.083</v>
@@ -6497,19 +9444,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.091</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="7">
@@ -6524,16 +9471,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -6551,16 +9498,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E8" t="n">
-        <v>233.3</v>
+        <v>266.7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -6578,7 +9525,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6605,16 +9552,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -6632,19 +9579,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="E11" t="n">
-        <v>39.5</v>
+        <v>38.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="12">
@@ -6659,7 +9606,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -6686,16 +9633,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -6713,16 +9660,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E14" t="n">
         <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -6740,7 +9687,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -6767,7 +9714,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6794,16 +9741,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -6821,16 +9768,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -6848,16 +9795,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -6875,16 +9822,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E20" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -6902,16 +9849,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -6929,7 +9876,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -6956,7 +9903,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -6983,16 +9930,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -7010,16 +9957,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E25" t="n">
         <v>600</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -7037,16 +9984,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -7064,16 +10011,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -7091,19 +10038,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="E28" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="G28" t="n">
-        <v>0.852</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="29">
@@ -7118,7 +10065,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -7145,16 +10092,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -7172,16 +10119,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6</v>
+        <v>-0.73</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -7199,7 +10146,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -7226,16 +10173,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -7253,7 +10200,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -7280,16 +10227,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E35" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G35" t="n">
         <v>1.25</v>
@@ -7307,19 +10254,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.429</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="37">
@@ -7334,7 +10281,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -7361,16 +10308,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -7388,16 +10335,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E39" t="n">
         <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -7415,19 +10362,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="E40" t="n">
-        <v>87.5</v>
+        <v>88.2</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G40" t="n">
-        <v>0.889</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="41">
@@ -7442,7 +10389,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -7469,16 +10416,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E42" t="n">
         <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -7496,16 +10443,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -7523,7 +10470,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -7550,16 +10497,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -7577,19 +10524,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="E46" t="n">
-        <v>23.5</v>
+        <v>25.9</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G46" t="n">
-        <v>0.864</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="47">
@@ -7604,16 +10551,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="E47" t="n">
         <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2</v>
+        <v>-0.27</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -7631,16 +10578,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E48" t="n">
         <v>200</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -7658,16 +10605,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="E49" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -7685,16 +10632,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E50" t="n">
-        <v>233.3</v>
+        <v>266.7</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -7712,7 +10659,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -7739,7 +10686,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -7766,16 +10713,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -7793,16 +10740,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -7820,16 +10767,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="E55" t="n">
-        <v>150</v>
+        <v>133.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2</v>
+        <v>-0.36</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -7847,16 +10794,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>1100</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -7874,7 +10821,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -7901,19 +10848,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E58" t="n">
-        <v>83.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="59">
@@ -7928,7 +10875,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -7955,7 +10902,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -7982,7 +10929,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -8009,7 +10956,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -8036,7 +10983,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -8063,7 +11010,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -8090,16 +11037,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E65" t="n">
         <v>120</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -8117,16 +11064,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -8144,7 +11091,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -8171,19 +11118,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="E68" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="69">
@@ -8198,19 +11145,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>43.5</v>
+        <v>55</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8</v>
+        <v>2.91</v>
       </c>
       <c r="G69" t="n">
-        <v>1.045</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="70">
@@ -8225,7 +11172,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -8252,16 +11199,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -8279,7 +11226,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -8306,16 +11253,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>76.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -8333,16 +11280,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E74" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -8360,19 +11307,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E75" t="n">
-        <v>63.6</v>
+        <v>61.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="G75" t="n">
-        <v>0.846</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="76">
@@ -8387,7 +11334,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -8414,16 +11361,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="E77" t="n">
-        <v>400</v>
+        <v>266.7</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -8441,16 +11388,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E78" t="n">
         <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -8468,7 +11415,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -8495,19 +11442,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="E80" t="n">
-        <v>29.4</v>
+        <v>27</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G80" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="81">
@@ -8522,7 +11469,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -8549,16 +11496,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -8576,19 +11523,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E83" t="n">
-        <v>150</v>
+        <v>133.3</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -8603,7 +11550,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -8630,16 +11577,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -8657,16 +11604,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E86" t="n">
         <v>150</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -8684,16 +11631,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -8711,19 +11658,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="E88" t="n">
-        <v>133.3</v>
+        <v>130</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G88" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="89">
@@ -8738,16 +11685,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="E89" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -8765,7 +11712,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -8792,7 +11739,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -8819,7 +11766,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -8846,16 +11793,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="E93" t="n">
-        <v>233.3</v>
+        <v>175</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -8873,16 +11820,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="E94" t="n">
         <v>133.3</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -8900,7 +11847,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -8927,16 +11874,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -8954,19 +11901,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D97" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="E97" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="F97" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G97" t="n">
-        <v>0.878</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="98">
@@ -8981,16 +11928,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -9008,7 +11955,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -9035,16 +11982,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D100" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G100" t="n">
         <v>1.25</v>
@@ -9062,16 +12009,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -9089,16 +12036,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -9116,7 +12063,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -9143,16 +12090,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -9170,16 +12117,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E105" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -9197,7 +12144,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -9224,16 +12171,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -9251,7 +12198,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -9278,16 +12225,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E109" t="n">
-        <v>36.4</v>
+        <v>45.5</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="G109" t="n">
         <v>1.1</v>
@@ -9305,16 +12252,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E110" t="n">
         <v>75</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G110" t="n">
         <v>2</v>
@@ -9332,7 +12279,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -9359,16 +12306,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -9386,7 +12333,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -9413,16 +12360,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -9440,19 +12387,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="E115" t="n">
-        <v>20</v>
+        <v>18.4</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G115" t="n">
-        <v>0.875</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="116">
@@ -9467,7 +12414,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -9494,7 +12441,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -9521,16 +12468,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D118" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="E118" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F118" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -9548,13 +12495,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -9575,7 +12522,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -9602,7 +12549,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -9629,16 +12576,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="F122" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -9656,16 +12603,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -9683,16 +12630,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -9710,19 +12657,19 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D125" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="E125" t="n">
-        <v>173.7</v>
+        <v>159.1</v>
       </c>
       <c r="F125" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="G125" t="n">
-        <v>1.583</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="126">
@@ -9737,7 +12684,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -9764,16 +12711,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D127" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -9791,10 +12738,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E128" t="n">
         <v>200</v>
@@ -9818,7 +12765,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -9845,16 +12792,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E130" t="n">
         <v>200</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -9872,7 +12819,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -9899,16 +12846,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -9926,7 +12873,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -9953,16 +12900,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E134" t="n">
-        <v>100</v>
+        <v>133.3</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G134" t="n">
         <v>1.5</v>
@@ -9980,16 +12927,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -10007,16 +12954,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="E136" t="n">
-        <v>155.6</v>
+        <v>177.8</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="G136" t="n">
         <v>1.8</v>
@@ -10034,19 +12981,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="E137" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="F137" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G137" t="n">
-        <v>0.881</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="138">
@@ -10061,19 +13008,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="E138" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="F138" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G138" t="n">
-        <v>0.916</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="139">
@@ -10088,16 +13035,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -10108,7 +13055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10192,22 +13139,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>83.2</v>
+        <v>85.5</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="G2" t="n">
-        <v>19.7</v>
+        <v>19.55</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.916</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="3">
@@ -10227,33 +13174,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>11.9</v>
+        <v>11.64</v>
       </c>
       <c r="H3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.881</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vienna Cream</t>
+          <t>Oat Milk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10262,33 +13209,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>83.5</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>0.64</v>
       </c>
       <c r="G4" t="n">
-        <v>15.1</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>Vienna Cream</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10297,22 +13244,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>82.8</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5</v>
+        <v>14.91</v>
       </c>
       <c r="H5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.878</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="6">
@@ -10323,7 +13270,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oat Milk</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10332,22 +13279,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>2.45</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>11.27</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.875</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="7">
@@ -10367,22 +13314,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79.3</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="H7" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.864</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="8">
@@ -10402,22 +13349,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="9">
@@ -10428,7 +13375,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10437,10 +13384,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -10463,7 +13410,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10472,10 +13419,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -10493,12 +13440,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10507,10 +13454,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -10528,12 +13475,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10542,10 +13489,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -10568,7 +13515,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10577,10 +13524,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -10598,12 +13545,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10612,10 +13559,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -10633,12 +13580,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10647,10 +13594,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -10668,12 +13615,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10682,10 +13629,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -10703,12 +13650,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10717,10 +13664,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -10743,7 +13690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10752,10 +13699,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -10778,7 +13725,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10787,10 +13734,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10808,7 +13755,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10822,10 +13769,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -10848,7 +13795,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10857,10 +13804,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -10883,7 +13830,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10892,10 +13839,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -10918,7 +13865,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10927,10 +13874,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -10948,12 +13895,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10962,10 +13909,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -10983,12 +13930,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10997,10 +13944,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -11018,12 +13965,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11032,10 +13979,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -11058,7 +14005,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11067,10 +14014,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -11088,12 +14035,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11102,10 +14049,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -11128,7 +14075,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11137,10 +14084,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -11158,12 +14105,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11172,10 +14119,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -11193,12 +14140,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11207,10 +14154,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -11233,7 +14180,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11242,10 +14189,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -11268,7 +14215,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11277,10 +14224,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -11303,7 +14250,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11312,10 +14259,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -11338,7 +14285,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11347,10 +14294,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -11373,7 +14320,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11382,10 +14329,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -11408,7 +14355,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11417,10 +14364,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -11452,10 +14399,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -11473,12 +14420,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11487,10 +14434,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -11513,7 +14460,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11522,10 +14469,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -11543,12 +14490,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11557,10 +14504,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -11578,12 +14525,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11592,10 +14539,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -11618,7 +14565,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11627,10 +14574,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -11648,12 +14595,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11662,10 +14609,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -11683,12 +14630,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -11697,10 +14644,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -11718,12 +14665,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11732,10 +14679,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -11753,12 +14700,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11767,10 +14714,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -11788,12 +14735,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11802,10 +14749,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -11828,7 +14775,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11837,10 +14784,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -11863,7 +14810,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11872,10 +14819,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -11898,7 +14845,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11907,10 +14854,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -11933,7 +14880,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11942,10 +14889,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -11968,7 +14915,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11977,10 +14924,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -11998,12 +14945,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12012,10 +14959,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -12038,7 +14985,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12047,10 +14994,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -12068,12 +15015,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Buttercream</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -12082,22 +15029,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>73.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="57">
@@ -12108,7 +15055,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Buttercream</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12117,22 +15064,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>74.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7</v>
+        <v>5.27</v>
       </c>
       <c r="G57" t="n">
-        <v>4.3</v>
+        <v>13.36</v>
       </c>
       <c r="H57" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="58">
@@ -12143,7 +15090,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12152,28 +15099,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>72.3</v>
+        <v>74.3</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="G58" t="n">
-        <v>1.1</v>
+        <v>0.73</v>
       </c>
       <c r="H58" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12187,22 +15134,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>71.8</v>
+        <v>74.3</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="G59" t="n">
-        <v>1.3</v>
+        <v>0.73</v>
       </c>
       <c r="H59" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="I59" t="n">
-        <v>1.083</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -12213,7 +15160,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>Almond Milk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12222,68 +15169,68 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>0.45</v>
       </c>
       <c r="G60" t="n">
-        <v>12.7</v>
+        <v>1.18</v>
       </c>
       <c r="H60" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>0.852</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12292,33 +15239,33 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>69.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="H62" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12327,22 +15274,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>69.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7</v>
+        <v>15.55</v>
       </c>
       <c r="H63" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="64">
@@ -12353,7 +15300,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12362,28 +15309,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>69.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>0.36</v>
       </c>
       <c r="G64" t="n">
-        <v>16.1</v>
+        <v>0.64</v>
       </c>
       <c r="H64" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>1.045</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12397,33 +15344,33 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>68.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="G65" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="H65" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="I65" t="n">
-        <v>1.091</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Almond Milk</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12432,33 +15379,33 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="G66" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>0.846</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12467,19 +15414,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="G67" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -12493,7 +15440,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12502,13 +15449,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>56.4</v>
+        <v>58.6</v>
       </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F68" t="n">
-        <v>1.1</v>
+        <v>0.18</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -12523,12 +15470,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12537,13 +15484,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>56.4</v>
+        <v>58.6</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -12563,7 +15510,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12572,13 +15519,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>56.4</v>
+        <v>58.6</v>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -12598,7 +15545,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -12607,13 +15554,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>56.4</v>
+        <v>58.6</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -12633,7 +15580,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -12642,13 +15589,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>56.4</v>
+        <v>58.6</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -12663,12 +15610,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -12677,19 +15624,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>56.4</v>
+        <v>56.9</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -12698,12 +15645,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12712,19 +15659,19 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>56.4</v>
+        <v>55.3</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -12738,7 +15685,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12747,22 +15694,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>56.2</v>
+        <v>53</v>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6</v>
+        <v>1.36</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="H75" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>1.429</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="76">
@@ -12773,7 +15720,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12782,22 +15729,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="G76" t="n">
-        <v>1.6</v>
+        <v>0.73</v>
       </c>
       <c r="H76" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="I76" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -12808,7 +15755,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12817,19 +15764,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>46.4</v>
+        <v>47.6</v>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -12838,12 +15785,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12852,19 +15799,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>46.4</v>
+        <v>47.6</v>
       </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -12878,7 +15825,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12887,19 +15834,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>46.4</v>
+        <v>47.6</v>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -12908,7 +15855,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12922,22 +15869,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>46.4</v>
+        <v>47.2</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="81">
@@ -12957,19 +15904,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>45.4</v>
+        <v>46.6</v>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I81" t="n">
         <v>2</v>
@@ -12978,12 +15925,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12992,19 +15939,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="H82" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -13027,19 +15974,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>44.2</v>
+        <v>45.3</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H83" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -13053,7 +16000,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -13062,19 +16009,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>44.2</v>
+        <v>45.3</v>
       </c>
       <c r="E84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F84" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G84" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H84" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -13088,7 +16035,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -13097,19 +16044,19 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>41.2</v>
+        <v>45.3</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H85" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -13123,7 +16070,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -13132,33 +16079,33 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>41.2</v>
+        <v>44.9</v>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3</v>
+        <v>0.91</v>
       </c>
       <c r="H86" t="n">
-        <v>1.53</v>
+        <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -13167,19 +16114,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -13193,7 +16140,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -13202,19 +16149,19 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H88" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -13223,12 +16170,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -13237,19 +16184,19 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="G89" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H89" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -13258,12 +16205,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -13272,19 +16219,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="G90" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H90" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -13298,7 +16245,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -13307,19 +16254,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H91" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -13333,7 +16280,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -13342,19 +16289,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="E92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H92" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -13368,101 +16315,101 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>39.3</v>
+        <v>42.2</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="G93" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="H93" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="I93" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>39.3</v>
+        <v>42.2</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="H94" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="I94" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>38.4</v>
+        <v>42.2</v>
       </c>
       <c r="E95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>1.2</v>
+        <v>0.73</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="H95" t="n">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -13473,66 +16420,66 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>36.4</v>
+        <v>40.4</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Paper Bag</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>36.4</v>
+        <v>40.4</v>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G97" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="98">
@@ -13543,7 +16490,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Paper Bag</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13552,19 +16499,19 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F98" t="n">
-        <v>5</v>
+        <v>0.82</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0.18</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -13578,7 +16525,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13587,19 +16534,19 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -13622,19 +16569,19 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -13657,19 +16604,19 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G101" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -13683,7 +16630,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -13692,19 +16639,19 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -13718,7 +16665,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -13727,19 +16674,19 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G103" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -13753,7 +16700,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -13762,19 +16709,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -13788,7 +16735,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13797,19 +16744,19 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1</v>
+        <v>1.82</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -13823,7 +16770,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13832,19 +16779,19 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G106" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -13853,12 +16800,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13867,19 +16814,19 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -13888,12 +16835,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13902,19 +16849,19 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>1.4</v>
+        <v>0.09</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8</v>
+        <v>0.09</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -13928,7 +16875,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13937,19 +16884,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E109" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="H109" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -13963,7 +16910,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -13972,19 +16919,19 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="G110" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H110" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -13998,7 +16945,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -14007,19 +16954,19 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2</v>
+        <v>1.36</v>
       </c>
       <c r="G111" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -14033,7 +16980,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -14042,19 +16989,19 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -14068,7 +17015,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -14077,19 +17024,19 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="G113" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -14103,7 +17050,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -14112,19 +17059,19 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -14138,7 +17085,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14147,19 +17094,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G115" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H115" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -14173,7 +17120,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mocha</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14182,19 +17129,19 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G116" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -14208,7 +17155,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14217,19 +17164,19 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H117" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -14243,7 +17190,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14252,19 +17199,19 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G118" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -14273,12 +17220,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Mocha</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -14287,19 +17234,19 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G119" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H119" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -14308,12 +17255,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -14322,19 +17269,19 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="H120" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -14357,19 +17304,19 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G121" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -14383,7 +17330,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -14392,19 +17339,19 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="G122" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -14413,12 +17360,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -14427,19 +17374,19 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -14453,7 +17400,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14462,19 +17409,19 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E124" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="G124" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -14488,7 +17435,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14497,19 +17444,19 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9</v>
+        <v>0.09</v>
       </c>
       <c r="G125" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -14523,7 +17470,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14532,19 +17479,19 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G126" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -14558,7 +17505,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14567,19 +17514,19 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1</v>
+        <v>0.91</v>
       </c>
       <c r="G127" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -14588,12 +17535,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14602,19 +17549,19 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -14628,7 +17575,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14637,19 +17584,19 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -14663,7 +17610,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14672,19 +17619,19 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G130" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H130" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -14698,7 +17645,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14707,19 +17654,19 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F131" t="n">
-        <v>0.8</v>
+        <v>0.18</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -14728,12 +17675,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14742,19 +17689,19 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G132" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -14777,19 +17724,19 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="E133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G133" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H133" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="I133" t="n">
         <v>1</v>
@@ -14798,12 +17745,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14812,22 +17759,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="E134" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5</v>
+        <v>3.18</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="135">
@@ -14838,7 +17785,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -14847,22 +17794,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>35.4</v>
+        <v>34.7</v>
       </c>
       <c r="E135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F135" t="n">
-        <v>3.3</v>
+        <v>0.36</v>
       </c>
       <c r="G135" t="n">
-        <v>1.9</v>
+        <v>0.27</v>
       </c>
       <c r="H135" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="I135" t="n">
-        <v>1.583</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="136">
@@ -14873,7 +17820,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14882,33 +17829,33 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>33.7</v>
+        <v>34.6</v>
       </c>
       <c r="E136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F136" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H136" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14917,33 +17864,33 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>33.6</v>
+        <v>34.1</v>
       </c>
       <c r="E137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F137" t="n">
-        <v>0.3</v>
+        <v>0.91</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H137" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -14955,19 +17902,19 @@
         <v>33</v>
       </c>
       <c r="E138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F138" t="n">
-        <v>0.9</v>
+        <v>1.45</v>
       </c>
       <c r="G138" t="n">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="H138" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="I138" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="139">
@@ -14978,7 +17925,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -14987,22 +17934,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31.8</v>
+        <v>27.2</v>
       </c>
       <c r="E139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F139" t="n">
-        <v>1.4</v>
+        <v>0.36</v>
       </c>
       <c r="G139" t="n">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="H139" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -18,8 +18,9 @@
     <sheet name="03-28" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="03-29" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="03-30" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accuracy Summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Confidence" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="03-31" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accuracy Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Confidence" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9275,6 +9276,2952 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" t="n">
+        <v>12</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>11</v>
+      </c>
+      <c r="D137" t="n">
+        <v>14</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>19</v>
+      </c>
+      <c r="D138" t="n">
+        <v>22</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9336,7 +12283,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -9363,16 +12310,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -9390,19 +12337,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>166.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -9417,19 +12364,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="E5" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="6">
@@ -9444,19 +12391,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="7">
@@ -9471,16 +12418,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -9498,16 +12445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
-        <v>266.7</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -9525,7 +12472,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -9552,16 +12499,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -9579,19 +12526,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="E11" t="n">
-        <v>38.3</v>
+        <v>37.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G11" t="n">
-        <v>0.922</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="12">
@@ -9606,7 +12553,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -9633,16 +12580,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -9660,16 +12607,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E14" t="n">
         <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -9687,7 +12634,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -9714,7 +12661,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -9741,16 +12688,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -9768,16 +12715,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E18" t="n">
         <v>150</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -9795,16 +12742,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="E19" t="n">
-        <v>187.5</v>
+        <v>212.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -9822,16 +12769,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="E20" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -9849,16 +12796,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -9876,7 +12823,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -9903,7 +12850,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -9930,16 +12877,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E24" t="n">
-        <v>83.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -9957,16 +12904,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E25" t="n">
         <v>600</v>
       </c>
       <c r="F25" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -9984,16 +12931,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -10011,16 +12958,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -10038,19 +12985,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="E28" t="n">
-        <v>39.5</v>
+        <v>39.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="n">
-        <v>0.913</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="29">
@@ -10065,7 +13012,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -10092,16 +13039,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -10119,16 +13066,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -10146,7 +13093,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -10173,16 +13120,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.18</v>
+        <v>-0.25</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -10200,7 +13147,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -10227,16 +13174,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E35" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F35" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G35" t="n">
         <v>1.25</v>
@@ -10254,19 +13201,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="E36" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G36" t="n">
-        <v>1.375</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37">
@@ -10281,7 +13228,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -10308,16 +13255,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -10335,16 +13282,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E39" t="n">
         <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -10362,19 +13309,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="E40" t="n">
-        <v>88.2</v>
+        <v>85</v>
       </c>
       <c r="F40" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="G40" t="n">
-        <v>0.85</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="41">
@@ -10389,7 +13336,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -10416,16 +13363,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E42" t="n">
         <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -10443,16 +13390,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -10470,7 +13417,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -10497,16 +13444,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -10524,19 +13471,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="E46" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G46" t="n">
-        <v>0.844</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="47">
@@ -10551,16 +13498,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E47" t="n">
         <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -10578,16 +13525,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E48" t="n">
         <v>200</v>
       </c>
       <c r="F48" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -10605,16 +13552,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E49" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F49" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -10632,16 +13579,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E50" t="n">
-        <v>266.7</v>
+        <v>300</v>
       </c>
       <c r="F50" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -10659,7 +13606,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -10686,7 +13633,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -10713,16 +13660,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="F53" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -10740,16 +13687,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -10767,16 +13714,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="E55" t="n">
         <v>133.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -10794,16 +13741,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E56" t="n">
         <v>1100</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -10821,7 +13768,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -10848,19 +13795,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E58" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G58" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="59">
@@ -10875,7 +13822,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -10902,7 +13849,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -10929,7 +13876,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -10956,7 +13903,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -10983,7 +13930,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -11010,7 +13957,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -11037,16 +13984,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E65" t="n">
         <v>120</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -11064,16 +14011,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -11091,7 +14038,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -11118,19 +14065,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D68" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="E68" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="F68" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="G68" t="n">
-        <v>0.906</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="69">
@@ -11145,19 +14092,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="E69" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="F69" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>0.91</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="70">
@@ -11172,7 +14119,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -11199,16 +14146,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -11226,7 +14173,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -11253,16 +14200,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E73" t="n">
-        <v>84.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F73" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -11280,16 +14227,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E74" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -11307,19 +14254,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="E75" t="n">
-        <v>61.5</v>
+        <v>57.1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G75" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -11334,7 +14281,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -11361,16 +14308,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E77" t="n">
-        <v>266.7</v>
+        <v>300</v>
       </c>
       <c r="F77" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -11388,16 +14335,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E78" t="n">
         <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -11415,7 +14362,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -11442,19 +14389,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="E80" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="F80" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G80" t="n">
-        <v>0.86</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="81">
@@ -11469,7 +14416,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -11496,16 +14443,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D82" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -11523,10 +14470,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D83" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E83" t="n">
         <v>133.3</v>
@@ -11550,7 +14497,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -11577,16 +14524,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -11604,16 +14551,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E86" t="n">
         <v>150</v>
       </c>
       <c r="F86" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -11631,16 +14578,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -11658,16 +14605,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="E88" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F88" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G88" t="n">
         <v>1.25</v>
@@ -11685,16 +14632,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="E89" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F89" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -11712,7 +14659,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -11739,7 +14686,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -11766,7 +14713,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -11793,16 +14740,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="E93" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F93" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -11820,16 +14767,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D94" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E94" t="n">
         <v>133.3</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -11847,7 +14794,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -11874,16 +14821,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D96" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -11901,19 +14848,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="E97" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="F97" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="G97" t="n">
-        <v>0.867</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="98">
@@ -11928,16 +14875,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D98" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -11955,7 +14902,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -11982,16 +14929,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D100" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F100" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="G100" t="n">
         <v>1.25</v>
@@ -12009,16 +14956,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D101" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -12036,16 +14983,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D102" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -12063,7 +15010,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -12090,16 +15037,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D104" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="E104" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F104" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -12117,16 +15064,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="E105" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F105" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -12144,7 +15091,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -12171,16 +15118,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D107" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -12198,7 +15145,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -12225,19 +15172,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E109" t="n">
-        <v>45.5</v>
+        <v>41.7</v>
       </c>
       <c r="F109" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="110">
@@ -12252,16 +15199,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D110" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E110" t="n">
         <v>75</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="G110" t="n">
         <v>2</v>
@@ -12279,7 +15226,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -12306,16 +15253,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D112" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -12333,7 +15280,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -12360,16 +15307,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D114" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -12387,19 +15334,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D115" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="E115" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="F115" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="G115" t="n">
-        <v>0.884</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="116">
@@ -12414,7 +15361,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -12441,7 +15388,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -12468,16 +15415,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D118" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E118" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F118" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -12495,13 +15442,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -12522,16 +15469,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -12549,7 +15496,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -12576,16 +15523,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="F122" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -12603,16 +15550,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D123" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -12630,16 +15577,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D124" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -12657,16 +15604,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D125" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="E125" t="n">
-        <v>159.1</v>
+        <v>172.7</v>
       </c>
       <c r="F125" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G125" t="n">
         <v>1.692</v>
@@ -12684,7 +15631,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -12711,16 +15658,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D127" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.45</v>
+        <v>-0.42</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -12738,10 +15685,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D128" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E128" t="n">
         <v>200</v>
@@ -12765,7 +15712,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -12792,16 +15739,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D130" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E130" t="n">
         <v>200</v>
       </c>
       <c r="F130" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -12819,7 +15766,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -12846,16 +15793,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="F132" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -12873,7 +15820,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -12900,19 +15847,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D134" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E134" t="n">
-        <v>133.3</v>
+        <v>100</v>
       </c>
       <c r="F134" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G134" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="135">
@@ -12927,16 +15874,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D135" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -12954,19 +15901,19 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D136" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="E136" t="n">
-        <v>177.8</v>
+        <v>154.5</v>
       </c>
       <c r="F136" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G136" t="n">
-        <v>1.8</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="137">
@@ -12981,19 +15928,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="E137" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="F137" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="G137" t="n">
-        <v>0.877</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="138">
@@ -13008,19 +15955,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D138" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="E138" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="F138" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="G138" t="n">
-        <v>0.915</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -13035,16 +15982,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D139" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -13055,7 +16002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13139,22 +16086,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85.5</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="G2" t="n">
-        <v>19.55</v>
+        <v>19.75</v>
       </c>
       <c r="H2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.915</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -13174,22 +16121,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83.8</v>
+        <v>86.2</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>11.64</v>
+        <v>11.83</v>
       </c>
       <c r="H3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.877</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="4">
@@ -13209,33 +16156,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.884</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vienna Cream</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13244,33 +16191,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="G5" t="n">
-        <v>14.91</v>
+        <v>11.33</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.906</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>Vienna Cream</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13279,22 +16226,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="G6" t="n">
-        <v>11.27</v>
+        <v>14.67</v>
       </c>
       <c r="H6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.867</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="7">
@@ -13314,22 +16261,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.844</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="8">
@@ -13349,33 +16296,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I8" t="n">
-        <v>0.86</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13384,19 +16331,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -13405,12 +16352,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13419,10 +16366,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -13445,7 +16392,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -13454,10 +16401,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -13475,12 +16422,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13489,10 +16436,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -13510,12 +16457,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13524,10 +16471,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -13550,7 +16497,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13559,10 +16506,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -13580,12 +16527,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13594,10 +16541,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -13620,7 +16567,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13629,10 +16576,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -13655,7 +16602,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13664,10 +16611,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -13690,7 +16637,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13699,10 +16646,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -13720,12 +16667,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13734,10 +16681,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -13755,12 +16702,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13769,10 +16716,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -13795,7 +16742,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13804,10 +16751,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -13830,7 +16777,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13839,10 +16786,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -13865,7 +16812,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13874,10 +16821,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -13895,12 +16842,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13909,10 +16856,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -13930,12 +16877,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13944,10 +16891,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -13970,7 +16917,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -13979,10 +16926,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -14005,7 +16952,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14014,10 +16961,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -14035,12 +16982,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -14049,10 +16996,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -14075,7 +17022,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14084,10 +17031,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -14105,12 +17052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14119,10 +17066,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -14140,12 +17087,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14154,10 +17101,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -14180,7 +17127,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14189,10 +17136,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -14210,12 +17157,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14224,10 +17171,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -14250,7 +17197,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14259,10 +17206,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -14285,7 +17232,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14294,10 +17241,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -14320,7 +17267,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14329,10 +17276,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -14355,7 +17302,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14364,10 +17311,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -14385,12 +17332,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14399,10 +17346,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -14425,7 +17372,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14434,10 +17381,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -14455,12 +17402,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14469,10 +17416,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -14495,7 +17442,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14504,10 +17451,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -14525,12 +17472,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14539,10 +17486,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -14560,12 +17507,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14574,10 +17521,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -14595,12 +17542,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14609,10 +17556,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -14630,12 +17577,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14644,10 +17591,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -14670,7 +17617,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14679,10 +17626,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -14705,7 +17652,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14714,10 +17661,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -14740,7 +17687,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14749,10 +17696,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -14770,12 +17717,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14784,10 +17731,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -14810,7 +17757,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14819,10 +17766,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -14840,12 +17787,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14854,10 +17801,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -14875,12 +17822,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14889,10 +17836,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -14915,7 +17862,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14924,10 +17871,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -14950,7 +17897,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14959,10 +17906,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -14985,7 +17932,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14994,10 +17941,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>76.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -15029,22 +17976,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>75.5</v>
+        <v>78</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G56" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="H56" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="I56" t="n">
-        <v>0.922</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="57">
@@ -15064,33 +18011,33 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>74.7</v>
+        <v>76.7</v>
       </c>
       <c r="E57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="G57" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="H57" t="n">
         <v>0.38</v>
       </c>
       <c r="I57" t="n">
-        <v>0.913</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>Almond Milk</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15099,22 +18046,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="G58" t="n">
-        <v>0.73</v>
+        <v>1.17</v>
       </c>
       <c r="H58" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="59">
@@ -15125,7 +18072,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15134,22 +18081,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
       <c r="E59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="G59" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="60">
@@ -15160,7 +18107,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Almond Milk</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15169,22 +18116,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="E60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="G60" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H60" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="I60" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="61">
@@ -15195,7 +18142,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15204,33 +18151,33 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>70.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Almond Milk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15239,22 +18186,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G62" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H62" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="I62" t="n">
-        <v>1.083</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -15274,22 +18221,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>66.8</v>
+        <v>67.7</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G63" t="n">
-        <v>15.55</v>
+        <v>14.83</v>
       </c>
       <c r="H63" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="I63" t="n">
-        <v>0.91</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="64">
@@ -15300,7 +18247,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15309,22 +18256,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>66</v>
+        <v>65.2</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="G64" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="65">
@@ -15335,7 +18282,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Almond Milk</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15344,22 +18291,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>64.90000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="E65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="G65" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="H65" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -15370,7 +18317,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15379,22 +18326,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>61.5</v>
+        <v>62.3</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="H66" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -15405,7 +18352,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15414,19 +18361,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>58.6</v>
+        <v>62.3</v>
       </c>
       <c r="E67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -15435,12 +18382,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15449,13 +18396,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="E68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F68" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -15470,12 +18417,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15484,13 +18431,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -15510,7 +18457,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15519,13 +18466,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="E70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -15554,13 +18501,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F71" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -15589,13 +18536,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -15610,12 +18557,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15624,19 +18571,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>56.9</v>
+        <v>60.7</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="G73" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -15650,7 +18597,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15659,22 +18606,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>55.3</v>
+        <v>58.2</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F74" t="n">
-        <v>0.45</v>
+        <v>1.42</v>
       </c>
       <c r="G74" t="n">
-        <v>0.55</v>
+        <v>1.67</v>
       </c>
       <c r="H74" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="75">
@@ -15685,7 +18632,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15694,22 +18641,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>53</v>
+        <v>55.5</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>1.36</v>
+        <v>0.42</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55</v>
+        <v>0.67</v>
       </c>
       <c r="H75" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>0.85</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="76">
@@ -15729,19 +18676,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>48.3</v>
+        <v>49.5</v>
       </c>
       <c r="E76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="G76" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="H76" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -15755,7 +18702,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15764,19 +18711,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="G77" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H77" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -15790,7 +18737,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -15799,19 +18746,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
       <c r="E78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="G78" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H78" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -15820,12 +18767,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -15834,19 +18781,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
       <c r="E79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F79" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G79" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H79" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -15860,7 +18807,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -15869,22 +18816,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="E80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F80" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G80" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="H80" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="I80" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -15895,7 +18842,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -15904,33 +18851,33 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>46.6</v>
+        <v>48.9</v>
       </c>
       <c r="E81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F81" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="G81" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H81" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -15939,22 +18886,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>45.3</v>
+        <v>47.9</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
-        <v>0.64</v>
+        <v>0.25</v>
       </c>
       <c r="G82" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H82" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -15974,19 +18921,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
       <c r="E83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F83" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G83" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="H83" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -16000,7 +18947,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16009,19 +18956,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F84" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G84" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="H84" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -16030,12 +18977,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -16044,33 +18991,33 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F85" t="n">
-        <v>0.36</v>
+        <v>1.17</v>
       </c>
       <c r="G85" t="n">
-        <v>0.36</v>
+        <v>0.83</v>
       </c>
       <c r="H85" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -16079,33 +19026,33 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>44.9</v>
+        <v>43.4</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>1.18</v>
+        <v>0.67</v>
       </c>
       <c r="G86" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="I86" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16114,19 +19061,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="G87" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H87" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -16135,12 +19082,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -16149,19 +19096,19 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F88" t="n">
-        <v>0.73</v>
+        <v>0.25</v>
       </c>
       <c r="G88" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H88" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -16170,12 +19117,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -16184,19 +19131,19 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F89" t="n">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="G89" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -16210,7 +19157,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16219,19 +19166,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F90" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="G90" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="H90" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -16240,12 +19187,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16254,19 +19201,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
-        <v>0.73</v>
+        <v>0.33</v>
       </c>
       <c r="G91" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="H91" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -16275,7 +19222,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -16289,19 +19236,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G92" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H92" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -16315,7 +19262,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16324,19 +19271,19 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G93" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H93" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -16345,12 +19292,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16359,19 +19306,19 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G94" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H94" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -16385,7 +19332,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16394,19 +19341,19 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>0.73</v>
+        <v>0.5</v>
       </c>
       <c r="G95" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="H95" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -16420,7 +19367,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -16429,22 +19376,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>40.4</v>
+        <v>42.9</v>
       </c>
       <c r="E96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F96" t="n">
-        <v>0.45</v>
+        <v>1.42</v>
       </c>
       <c r="G96" t="n">
-        <v>0.45</v>
+        <v>0.92</v>
       </c>
       <c r="H96" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="I96" t="n">
-        <v>1.25</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="97">
@@ -16464,19 +19411,19 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>40.4</v>
+        <v>41.6</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F97" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G97" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H97" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="I97" t="n">
         <v>1.25</v>
@@ -16490,31 +19437,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Paper Bag</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>38.6</v>
+        <v>41.6</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98" t="n">
-        <v>0.82</v>
+        <v>0.33</v>
       </c>
       <c r="G98" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H98" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="99">
@@ -16525,31 +19472,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>38.6</v>
+        <v>41.6</v>
       </c>
       <c r="E99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F99" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="G99" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H99" t="n">
-        <v>2.12</v>
+        <v>1.54</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="100">
@@ -16565,23 +19512,23 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F100" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G100" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -16595,28 +19542,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F101" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G101" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H101" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -16630,28 +19577,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="G102" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H102" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -16670,23 +19617,23 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F103" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G103" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H103" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -16700,28 +19647,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Paper Bag</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>0.09</v>
+        <v>0.83</v>
       </c>
       <c r="G104" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H104" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -16740,23 +19687,23 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F105" t="n">
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="H105" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -16770,28 +19717,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F106" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="G106" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H106" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -16805,28 +19752,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F107" t="n">
-        <v>0.09</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H107" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -16840,28 +19787,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F108" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G108" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H108" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -16870,33 +19817,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="G109" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="H109" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -16905,33 +19852,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F110" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="G110" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H110" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -16940,33 +19887,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>1.36</v>
+        <v>0.08</v>
       </c>
       <c r="G111" t="n">
-        <v>0.73</v>
+        <v>0.08</v>
       </c>
       <c r="H111" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -16980,28 +19927,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F112" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="G112" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H112" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -17015,28 +19962,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F113" t="n">
-        <v>0.55</v>
+        <v>0.08</v>
       </c>
       <c r="G113" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H113" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -17050,28 +19997,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F114" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="G114" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H114" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -17085,28 +20032,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F115" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G115" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H115" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -17120,28 +20067,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F116" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G116" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H116" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -17160,23 +20107,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F117" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G117" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H117" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -17195,23 +20142,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F118" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G118" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H118" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -17230,23 +20177,23 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F119" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G119" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H119" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -17255,33 +20202,33 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F120" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G120" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H120" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -17300,23 +20247,23 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F121" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G121" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H121" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -17330,28 +20277,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F122" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H122" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -17360,33 +20307,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F123" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="G123" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H123" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -17395,33 +20342,33 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E124" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F124" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="G124" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H124" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -17430,33 +20377,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E125" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F125" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G125" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H125" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -17470,28 +20417,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E126" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F126" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G126" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H126" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -17505,28 +20452,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F127" t="n">
-        <v>0.91</v>
+        <v>0.17</v>
       </c>
       <c r="G127" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H127" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -17535,33 +20482,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E128" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F128" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G128" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H128" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -17575,28 +20522,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F129" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="G129" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H129" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -17610,28 +20557,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F130" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G130" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H130" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -17645,28 +20592,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F131" t="n">
-        <v>0.18</v>
+        <v>0.92</v>
       </c>
       <c r="G131" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H131" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -17680,28 +20627,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F132" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G132" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H132" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -17715,28 +20662,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="E133" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F133" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G133" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H133" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="I133" t="n">
         <v>1</v>
@@ -17750,112 +20697,112 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>36.9</v>
+        <v>40.7</v>
       </c>
       <c r="E134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F134" t="n">
-        <v>3.18</v>
+        <v>0.08</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="H134" t="n">
-        <v>1.13</v>
+        <v>3.32</v>
       </c>
       <c r="I134" t="n">
-        <v>1.692</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>34.7</v>
+        <v>40.7</v>
       </c>
       <c r="E135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F135" t="n">
-        <v>0.36</v>
+        <v>1.42</v>
       </c>
       <c r="G135" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="H135" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>34.6</v>
+        <v>40.3</v>
       </c>
       <c r="E136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F136" t="n">
-        <v>0.27</v>
+        <v>0.83</v>
       </c>
       <c r="G136" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="H136" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -17864,22 +20811,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>34.1</v>
+        <v>38.2</v>
       </c>
       <c r="E137" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F137" t="n">
-        <v>0.91</v>
+        <v>3.17</v>
       </c>
       <c r="G137" t="n">
-        <v>0.45</v>
+        <v>1.83</v>
       </c>
       <c r="H137" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>1.667</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="138">
@@ -17890,7 +20837,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -17899,22 +20846,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>33</v>
+        <v>35.8</v>
       </c>
       <c r="E138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F138" t="n">
-        <v>1.45</v>
+        <v>0.25</v>
       </c>
       <c r="G138" t="n">
-        <v>0.82</v>
+        <v>0.33</v>
       </c>
       <c r="H138" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -17934,19 +20881,19 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>27.2</v>
+        <v>28.4</v>
       </c>
       <c r="E139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F139" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G139" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H139" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I139" t="n">
         <v>2</v>

--- a/output/feedback_report.xlsx
+++ b/output/feedback_report.xlsx
@@ -19,8 +19,9 @@
     <sheet name="03-29" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="03-30" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="03-31" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Accuracy Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Confidence" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="04-01" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Accuracy Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Confidence" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12222,6 +12223,2952 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>14</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>20</v>
+      </c>
+      <c r="D69" t="n">
+        <v>24</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Gardena</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10oz Hot Cup</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2 Cup Carrier</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2% Milk</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agave Cases</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Beverage Napkin</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Black Straws</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Black Trash Bag</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Buttercream</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cafiza</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cinnamon Powder</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cocoa Box</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Coldbrew Concentrate</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cup Carriers</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Green</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cup Sleeves - Red</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Custom 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Custom 4 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Custom Ice Cups</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Decaf Beans</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Dish Detergent</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Espresso Beans</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>14</v>
+      </c>
+      <c r="D97" t="n">
+        <v>16</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Espresso Trash Bag</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Forks</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hot Lid</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ice Cups</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ice lid</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jasmine Tea Bag</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lid Plug</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>M1200 Matcha</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Matcha Drizzle</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Mirado (retail)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mocha</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Musco Syrup</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Paper 2 Cup Carrier Bag</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Paper Bag</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Paper Towel</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Passionfruit Puree</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pastry Bag, Brown</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Receipt rolls</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Rinza</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sanchez (retail)</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Scarlet Tea</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Cases</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sugar Tub</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sugar in the raw</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supremo (retail)</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tea Bag</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Toilet Paper</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Toilet Solution</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tonic Water</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ube Condensed Milk</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vanilla Syrup</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Vienna Cream</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>13</v>
+      </c>
+      <c r="D137" t="n">
+        <v>12</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Whole Milk</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>22</v>
+      </c>
+      <c r="D138" t="n">
+        <v>22</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>KTOWN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Wooden Stir Stick</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12283,7 +15230,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -12310,7 +15257,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>0.08</v>
@@ -12337,19 +15284,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="E4" t="n">
-        <v>166.7</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="5">
@@ -12364,16 +15311,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="G5" t="n">
         <v>1.077</v>
@@ -12391,19 +15338,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>35.7</v>
+        <v>31.2</v>
       </c>
       <c r="F6" t="n">
         <v>0.08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.077</v>
+        <v>1.067</v>
       </c>
     </row>
     <row r="7">
@@ -12418,16 +15365,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -12445,16 +15392,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="F8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -12472,16 +15419,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -12499,16 +15446,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -12526,19 +15473,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="E11" t="n">
-        <v>37.3</v>
+        <v>34.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="G11" t="n">
-        <v>0.911</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="12">
@@ -12553,7 +15500,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -12580,16 +15527,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -12607,16 +15554,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -12634,7 +15581,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12661,7 +15608,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12688,7 +15635,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>0.08</v>
@@ -12715,10 +15662,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E18" t="n">
         <v>150</v>
@@ -12742,19 +15689,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="E19" t="n">
-        <v>212.5</v>
+        <v>166.7</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>0.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -12769,16 +15716,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E20" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -12796,7 +15743,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
         <v>0.08</v>
@@ -12823,7 +15770,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12850,7 +15797,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -12877,16 +15824,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E24" t="n">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -12904,16 +15851,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="E25" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="F25" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -12931,16 +15878,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -12958,16 +15905,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -12985,19 +15932,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="G28" t="n">
-        <v>0.902</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="29">
@@ -13012,7 +15959,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -13039,16 +15986,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -13066,16 +16013,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.67</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -13093,7 +16040,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -13120,16 +16067,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -13147,16 +16094,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -13174,16 +16121,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="E35" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F35" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="G35" t="n">
         <v>1.25</v>
@@ -13201,19 +16148,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="E36" t="n">
-        <v>58.3</v>
+        <v>57.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.2</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="37">
@@ -13228,7 +16175,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13255,16 +16202,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -13282,16 +16229,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E39" t="n">
         <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -13309,16 +16256,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="E40" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F40" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="G40" t="n">
         <v>0.952</v>
@@ -13336,7 +16283,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13363,7 +16310,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
         <v>0.08</v>
@@ -13390,16 +16337,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -13417,7 +16364,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13444,16 +16391,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -13471,19 +16418,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D46" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="E46" t="n">
-        <v>26.3</v>
+        <v>28.1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="47">
@@ -13498,16 +16445,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="E47" t="n">
         <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -13525,16 +16472,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E48" t="n">
         <v>200</v>
       </c>
       <c r="F48" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -13552,16 +16499,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="E49" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="F49" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -13579,16 +16526,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="E50" t="n">
-        <v>300</v>
+        <v>333.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -13606,7 +16553,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13633,7 +16580,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -13660,16 +16607,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="F53" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -13687,16 +16634,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -13714,16 +16661,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
         <v>133.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -13741,16 +16688,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>0.92</v>
+        <v>1.38</v>
       </c>
       <c r="E56" t="n">
-        <v>1100</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -13768,7 +16715,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -13795,19 +16742,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E58" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="F58" t="n">
         <v>-0.08</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59">
@@ -13822,7 +16769,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -13849,7 +16796,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -13876,7 +16823,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -13903,7 +16850,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -13930,7 +16877,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -13957,7 +16904,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -13984,16 +16931,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="E65" t="n">
-        <v>120</v>
+        <v>116.7</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.33</v>
+        <v>-0.38</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -14011,16 +16958,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D66" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -14038,7 +16985,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -14065,19 +17012,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D68" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="E68" t="n">
-        <v>24.4</v>
+        <v>23</v>
       </c>
       <c r="F68" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G68" t="n">
-        <v>0.893</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="69">
@@ -14092,19 +17039,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D69" t="n">
-        <v>8.42</v>
+        <v>8.08</v>
       </c>
       <c r="E69" t="n">
-        <v>56.7</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="G69" t="n">
-        <v>0.881</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="70">
@@ -14119,7 +17066,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -14146,7 +17093,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D71" t="n">
         <v>0.08</v>
@@ -14173,7 +17120,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -14200,19 +17147,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D73" t="n">
         <v>0.92</v>
       </c>
       <c r="E73" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="F73" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="74">
@@ -14227,16 +17174,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D74" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="E74" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="F74" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -14254,19 +17201,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>57.1</v>
+        <v>56.2</v>
       </c>
       <c r="F75" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9330000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -14281,7 +17228,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -14308,16 +17255,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D77" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="E77" t="n">
-        <v>300</v>
+        <v>333.3</v>
       </c>
       <c r="F77" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -14335,7 +17282,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D78" t="n">
         <v>0.08</v>
@@ -14362,7 +17309,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -14389,19 +17336,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D80" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>27.5</v>
+        <v>31</v>
       </c>
       <c r="F80" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>0.851</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="81">
@@ -14416,7 +17363,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -14443,16 +17390,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D82" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -14470,13 +17417,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D83" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E83" t="n">
-        <v>133.3</v>
+        <v>100</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -14497,7 +17444,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -14524,7 +17471,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D85" t="n">
         <v>0.08</v>
@@ -14551,19 +17498,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E86" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
         <v>0.08</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="87">
@@ -14578,16 +17525,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -14605,16 +17552,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D88" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="E88" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F88" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G88" t="n">
         <v>1.25</v>
@@ -14632,16 +17579,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="E89" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="F89" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -14659,7 +17606,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -14686,7 +17633,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -14713,7 +17660,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -14740,16 +17687,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D93" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="E93" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F93" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -14767,19 +17714,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E94" t="n">
-        <v>133.3</v>
+        <v>100</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -14794,7 +17741,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -14821,7 +17768,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D96" t="n">
         <v>0.08</v>
@@ -14848,19 +17795,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D97" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="E97" t="n">
-        <v>20.6</v>
+        <v>19.7</v>
       </c>
       <c r="F97" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="G97" t="n">
-        <v>0.883</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="98">
@@ -14875,7 +17822,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D98" t="n">
         <v>0.08</v>
@@ -14902,7 +17849,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -14929,19 +17876,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D100" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="E100" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="G100" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="101">
@@ -14956,7 +17903,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D101" t="n">
         <v>0.08</v>
@@ -14983,16 +17930,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D102" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.25</v>
+        <v>-0.38</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -15010,7 +17957,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -15037,16 +17984,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D104" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="E104" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F104" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -15064,16 +18011,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D105" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="E105" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="F105" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -15091,7 +18038,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -15118,16 +18065,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D107" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -15145,7 +18092,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -15172,19 +18119,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D109" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E109" t="n">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="F109" t="n">
         <v>0.08</v>
       </c>
       <c r="G109" t="n">
-        <v>1.091</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="110">
@@ -15199,16 +18146,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="E110" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="G110" t="n">
         <v>2</v>
@@ -15226,7 +18173,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -15253,16 +18200,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -15280,7 +18227,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -15307,7 +18254,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D114" t="n">
         <v>0.08</v>
@@ -15334,19 +18281,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D115" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F115" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="G115" t="n">
-        <v>0.913</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="116">
@@ -15361,7 +18308,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -15388,7 +18335,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -15415,16 +18362,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D118" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="E118" t="n">
-        <v>500</v>
+        <v>333.3</v>
       </c>
       <c r="F118" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -15442,16 +18389,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E119" t="n">
         <v>1200</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -15469,7 +18416,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D120" t="n">
         <v>0.08</v>
@@ -15496,7 +18443,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -15523,16 +18470,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="F122" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -15550,7 +18497,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D123" t="n">
         <v>0.08</v>
@@ -15577,16 +18524,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D124" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -15604,16 +18551,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D125" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="E125" t="n">
-        <v>172.7</v>
+        <v>200</v>
       </c>
       <c r="F125" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
         <v>1.692</v>
@@ -15631,7 +18578,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -15658,16 +18605,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D127" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E127" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.42</v>
+        <v>-0.31</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -15685,16 +18632,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D128" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="E128" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -15712,7 +18659,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -15739,16 +18686,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D130" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E130" t="n">
         <v>200</v>
       </c>
       <c r="F130" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -15766,7 +18713,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -15793,16 +18740,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="F132" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -15820,7 +18767,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -15847,19 +18794,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D134" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E134" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F134" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G134" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="135">
@@ -15874,16 +18821,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D135" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -15901,16 +18848,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D136" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="E136" t="n">
-        <v>154.5</v>
+        <v>181.8</v>
       </c>
       <c r="F136" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="G136" t="n">
         <v>1.375</v>
@@ -15928,19 +18875,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D137" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="E137" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="F137" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G137" t="n">
-        <v>0.904</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="138">
@@ -15955,19 +18902,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D138" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="E138" t="n">
-        <v>14.8</v>
+        <v>13.5</v>
       </c>
       <c r="F138" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -15982,7 +18929,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D139" t="n">
         <v>0.08</v>
@@ -16002,7 +18949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16086,22 +19033,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>90.7</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="G2" t="n">
-        <v>19.75</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -16121,22 +19068,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>86.2</v>
+        <v>88.8</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="G3" t="n">
-        <v>11.83</v>
+        <v>11.85</v>
       </c>
       <c r="H3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.904</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="4">
@@ -16147,7 +19094,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oat Milk</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16156,22 +19103,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.67</v>
+        <v>2.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>11.69</v>
       </c>
       <c r="H4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.913</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="5">
@@ -16182,7 +19129,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>Oat Milk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16191,22 +19138,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>2.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>11.33</v>
+        <v>3.46</v>
       </c>
       <c r="H5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.883</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -16226,22 +19173,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="G6" t="n">
-        <v>14.67</v>
+        <v>14.69</v>
       </c>
       <c r="H6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.893</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="7">
@@ -16261,22 +19208,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="H7" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.838</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="8">
@@ -16296,33 +19243,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="H8" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.851</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Buttercream</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16331,33 +19278,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78.3</v>
+        <v>81.3</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>0.25</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>4.23</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16366,10 +19313,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -16392,7 +19339,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16401,10 +19348,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -16422,12 +19369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Vanilla Syrup</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -16436,10 +19383,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -16457,12 +19404,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Toilet Solution</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -16471,10 +19418,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -16497,7 +19444,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -16506,10 +19453,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -16527,12 +19474,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -16541,10 +19488,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -16562,12 +19509,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -16576,10 +19523,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -16597,12 +19544,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -16611,10 +19558,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -16637,7 +19584,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -16646,10 +19593,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -16672,7 +19619,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -16681,10 +19628,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -16707,7 +19654,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -16716,10 +19663,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -16742,7 +19689,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vanilla Syrup</t>
+          <t>Pastry Bag, Brown</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -16751,10 +19698,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -16777,7 +19724,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toilet Solution</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -16786,10 +19733,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -16812,7 +19759,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -16821,10 +19768,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -16842,12 +19789,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -16856,10 +19803,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -16877,12 +19824,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -16891,10 +19838,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -16917,7 +19864,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -16926,10 +19873,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -16952,7 +19899,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tea Bag</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16961,10 +19908,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -16982,12 +19929,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -16996,10 +19943,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -17022,7 +19969,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Cinnamon Powder</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -17031,10 +19978,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -17052,12 +19999,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scarlet Tea</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -17066,10 +20013,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -17087,12 +20034,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Musco Syrup</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -17101,10 +20048,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -17127,7 +20074,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cinnamon Powder</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -17136,10 +20083,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -17157,12 +20104,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -17171,10 +20118,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -17206,10 +20153,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -17232,7 +20179,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -17241,10 +20188,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -17267,7 +20214,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jasmine Tea Bag</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -17276,10 +20223,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -17302,7 +20249,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hot Lid</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -17311,10 +20258,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -17332,12 +20279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -17346,10 +20293,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -17372,7 +20319,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Musco Syrup</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -17381,10 +20328,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -17402,12 +20349,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cafiza</t>
+          <t>Scarlet Tea</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -17416,10 +20363,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -17442,7 +20389,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -17451,10 +20398,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -17486,10 +20433,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -17507,12 +20454,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Tea Bag</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -17521,10 +20468,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -17542,12 +20489,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pastry Bag, Brown</t>
+          <t>Custom 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17556,10 +20503,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -17577,12 +20524,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17591,10 +20538,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -17612,12 +20559,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17626,10 +20573,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -17652,7 +20599,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Custom 2 Cup Carrier Bag</t>
+          <t>Jasmine Tea Bag</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17661,10 +20608,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -17682,12 +20629,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Custom 4 Cup Carrier Bag</t>
+          <t>Sugar in the raw</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17696,10 +20643,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -17717,12 +20664,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Custom 4 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17731,10 +20678,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17752,12 +20699,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Cafiza</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17766,10 +20713,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -17801,10 +20748,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -17822,12 +20769,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17836,10 +20783,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -17862,7 +20809,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17871,10 +20818,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -17897,7 +20844,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Almond Milk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17906,22 +20853,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>78.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.067</v>
       </c>
     </row>
     <row r="55">
@@ -17932,7 +20879,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sugar in the raw</t>
+          <t>Espresso Beans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17941,33 +20888,33 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>12.77</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Buttercream</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17976,33 +20923,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
-        <v>1.58</v>
+        <v>0.38</v>
       </c>
       <c r="G56" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="I56" t="n">
-        <v>0.911</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Espresso Beans</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -18011,28 +20958,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>76.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F57" t="n">
-        <v>5.08</v>
+        <v>0.31</v>
       </c>
       <c r="G57" t="n">
-        <v>13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="I57" t="n">
-        <v>0.902</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -18046,33 +20993,33 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>75.2</v>
+        <v>72.5</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F58" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="I58" t="n">
-        <v>1.077</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18081,22 +21028,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>74</v>
+        <v>72.2</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F59" t="n">
-        <v>0.42</v>
+        <v>8.08</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>15.54</v>
       </c>
       <c r="H59" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="I59" t="n">
-        <v>1.091</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="60">
@@ -18107,31 +21054,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agave Cases</t>
+          <t>Cup Sleeves - Green</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F60" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="G60" t="n">
-        <v>1.17</v>
+        <v>0.62</v>
       </c>
       <c r="H60" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="I60" t="n">
-        <v>1.077</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -18147,23 +21094,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>71.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F61" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="G61" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H61" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -18172,12 +21119,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Almond Milk</t>
+          <t>Agave Cases</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18186,22 +21133,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>68.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F62" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="H62" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="63">
@@ -18212,7 +21159,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
+          <t>Ice lid</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18221,33 +21168,33 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>67.7</v>
+        <v>67</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
-        <v>8.42</v>
+        <v>0.62</v>
       </c>
       <c r="G63" t="n">
-        <v>14.83</v>
+        <v>1.08</v>
       </c>
       <c r="H63" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I63" t="n">
-        <v>0.881</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ice lid</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18256,33 +21203,33 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>65.2</v>
+        <v>67</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="H64" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18291,19 +21238,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>63.4</v>
+        <v>62.9</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F65" t="n">
-        <v>0.92</v>
+        <v>0.08</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -18317,7 +21264,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Green</t>
+          <t>Mirado (retail)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18326,19 +21273,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
       <c r="G66" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -18352,7 +21299,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18361,19 +21308,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="G67" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -18387,7 +21334,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Supremo (retail)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18396,13 +21343,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>60.7</v>
+        <v>62.9</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -18422,7 +21369,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mirado (retail)</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18431,22 +21378,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>60.7</v>
+        <v>62.2</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F69" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
@@ -18457,7 +21404,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18466,19 +21413,19 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>60.7</v>
+        <v>58.6</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F70" t="n">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -18487,12 +21434,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supremo (retail)</t>
+          <t>M1200 Matcha</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18501,22 +21448,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>60.7</v>
+        <v>56</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F71" t="n">
-        <v>0.17</v>
+        <v>1.46</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="72">
@@ -18527,7 +21474,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18536,33 +21483,33 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>60.7</v>
+        <v>54.6</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72" t="n">
-        <v>0.92</v>
+        <v>0.23</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paper 4 Cup Carrier Bag - Tamper Resistant</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18571,22 +21518,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>60.7</v>
+        <v>53.5</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="74">
@@ -18597,7 +21544,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>M1200 Matcha</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18606,22 +21553,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>58.2</v>
+        <v>52.4</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F74" t="n">
-        <v>1.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>1.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.71</v>
+        <v>1.04</v>
       </c>
       <c r="I74" t="n">
-        <v>0.952</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -18632,7 +21579,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Tonic Water</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18641,33 +21588,33 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>55.5</v>
+        <v>52.1</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F75" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="G75" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Strawberry Puree Cases</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18676,19 +21623,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F76" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="G76" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -18711,19 +21658,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>48.9</v>
+        <v>50.2</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="G77" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H77" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -18737,7 +21684,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Strawberry Puree Cases</t>
+          <t>Custom Ice Cups</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -18746,19 +21693,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>48.9</v>
+        <v>50.2</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F78" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="G78" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H78" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -18767,12 +21714,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Custom Ice Cups</t>
+          <t>Beverage Napkin</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -18781,19 +21728,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>48.9</v>
+        <v>50.2</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F79" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="G79" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -18807,7 +21754,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -18816,19 +21763,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H80" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -18842,7 +21789,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Beverage Napkin</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -18851,19 +21798,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F81" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="G81" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="H81" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -18877,7 +21824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Bleach</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18889,19 +21836,19 @@
         <v>47.9</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="G82" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H82" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -18912,7 +21859,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Paper 2 Cup Carrier Bag</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -18921,19 +21868,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>46.6</v>
+        <v>47.9</v>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F83" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="G83" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H83" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -18947,7 +21894,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18956,19 +21903,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>46.6</v>
+        <v>47.9</v>
       </c>
       <c r="E84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F84" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="G84" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H84" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -18977,12 +21924,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18991,33 +21938,33 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>46.2</v>
+        <v>47.9</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F85" t="n">
-        <v>1.17</v>
+        <v>0.31</v>
       </c>
       <c r="G85" t="n">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="I85" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -19026,33 +21973,33 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>43.4</v>
+        <v>47.5</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86" t="n">
-        <v>0.67</v>
+        <v>1.15</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H86" t="n">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Paper Towel</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19061,19 +22008,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>43.4</v>
+        <v>46.6</v>
       </c>
       <c r="E87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="G87" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H87" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -19082,12 +22029,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Half &amp; Half</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -19096,22 +22043,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>43.4</v>
+        <v>46.1</v>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F88" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="G88" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H88" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="89">
@@ -19122,7 +22069,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>2% Milk</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19131,22 +22078,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F89" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G89" t="n">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="H89" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="90">
@@ -19157,7 +22104,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paper 2 Cup Carrier Bag</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -19166,19 +22113,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="G90" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H90" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -19187,12 +22134,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -19201,19 +22148,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
-        <v>0.33</v>
+        <v>0.62</v>
       </c>
       <c r="G91" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H91" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -19227,7 +22174,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Black Straws</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -19236,19 +22183,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="G92" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H92" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -19257,12 +22204,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Black Straws</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -19271,19 +22218,19 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F93" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="G93" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H93" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -19292,7 +22239,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -19306,19 +22253,19 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="G94" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H94" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -19327,12 +22274,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Paper Bag</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -19341,19 +22288,19 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H95" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -19376,19 +22323,19 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>42.9</v>
+        <v>44.2</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F96" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="G96" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="H96" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="I96" t="n">
         <v>1.375</v>
@@ -19397,12 +22344,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ice Cups</t>
+          <t>Sugar Tub</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -19411,22 +22358,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>41.6</v>
+        <v>42.9</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F97" t="n">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="G97" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="H97" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="I97" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -19437,7 +22384,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tonic Water</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19446,22 +22393,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>41.6</v>
+        <v>42.9</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F98" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="G98" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="H98" t="n">
-        <v>1.41</v>
+        <v>3.46</v>
       </c>
       <c r="I98" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -19472,7 +22419,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Half &amp; Half</t>
+          <t>Mocha</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -19481,22 +22428,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>41.6</v>
+        <v>42.9</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="G99" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="H99" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="I99" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -19507,7 +22454,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mocha</t>
+          <t>Rinza</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19516,19 +22463,19 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F100" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G100" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H100" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -19542,7 +22489,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -19551,19 +22498,19 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F101" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G101" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H101" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -19577,7 +22524,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rinza</t>
+          <t>Ube Condensed Milk</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -19586,19 +22533,19 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G102" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H102" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -19612,7 +22559,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Paper Towel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -19621,19 +22568,19 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F103" t="n">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
       <c r="G103" t="n">
         <v>0.08</v>
       </c>
       <c r="H103" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -19647,7 +22594,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Paper Bag</t>
+          <t>Passionfruit Puree</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -19656,19 +22603,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F104" t="n">
-        <v>0.83</v>
+        <v>0.08</v>
       </c>
       <c r="G104" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H104" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -19691,19 +22638,19 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F105" t="n">
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="H105" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -19717,7 +22664,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Passionfruit Puree</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -19726,19 +22673,19 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F106" t="n">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H106" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -19752,7 +22699,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>10oz Hot Cup</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -19761,19 +22708,19 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="G107" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H107" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -19787,7 +22734,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sugar Tub</t>
+          <t>Hand Soap</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19796,19 +22743,19 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F108" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G108" t="n">
         <v>0.08</v>
       </c>
       <c r="H108" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -19817,12 +22764,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ube Condensed Milk</t>
+          <t>Receipt rolls</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19831,19 +22778,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F109" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H109" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -19852,12 +22799,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>10oz Hot Cup</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19866,10 +22813,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F110" t="n">
         <v>0.08</v>
@@ -19878,7 +22825,7 @@
         <v>0.08</v>
       </c>
       <c r="H110" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -19887,12 +22834,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wooden Stir Stick</t>
+          <t>Condensed Milk</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19901,19 +22848,19 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="G111" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H111" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -19927,7 +22874,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Condensed Milk</t>
+          <t>Cup Sleeves - Red</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19936,19 +22883,19 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F112" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G112" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H112" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -19962,7 +22909,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cup Sleeves - Red</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19971,19 +22918,19 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F113" t="n">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="G113" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H113" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -19997,7 +22944,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Decaf Beans</t>
+          <t>Dish Detergent</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20006,19 +22953,19 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="G114" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H114" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -20032,7 +22979,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dish Detergent</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20041,19 +22988,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G115" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H115" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -20067,7 +23014,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Hot Lid</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -20076,19 +23023,19 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F116" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G116" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H116" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -20102,7 +23049,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Ice Cups</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20111,22 +23058,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F117" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="G117" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="H117" t="n">
-        <v>3.32</v>
+        <v>1.62</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="118">
@@ -20137,7 +23084,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lid Plug</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20146,19 +23093,19 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F118" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G118" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H118" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -20172,7 +23119,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mocha</t>
+          <t>Lid Plug</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20181,19 +23128,19 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F119" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G119" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H119" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -20207,7 +23154,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nitrile Gloves</t>
+          <t>Mocha</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20216,19 +23163,19 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="G120" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H120" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -20242,7 +23189,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Paper Bag</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -20251,19 +23198,19 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F121" t="n">
-        <v>0.83</v>
+        <v>0.15</v>
       </c>
       <c r="G121" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H121" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -20272,12 +23219,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Receipt rolls</t>
+          <t>Espresso Trash Bag</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -20286,19 +23233,19 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="G122" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="H122" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -20307,12 +23254,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Paper Bag</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20321,19 +23268,19 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>0.08</v>
+        <v>0.85</v>
       </c>
       <c r="G123" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H123" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -20356,19 +23303,19 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F124" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G124" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H124" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -20382,7 +23329,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2 Cup Carrier</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20391,19 +23338,19 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F125" t="n">
-        <v>0.08</v>
+        <v>1.38</v>
       </c>
       <c r="G125" t="n">
-        <v>0.08</v>
+        <v>0.62</v>
       </c>
       <c r="H125" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -20412,12 +23359,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Black Trash Bag</t>
+          <t>2 Cup Carrier</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20426,10 +23373,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F126" t="n">
         <v>0.08</v>
@@ -20438,7 +23385,7 @@
         <v>0.08</v>
       </c>
       <c r="H126" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -20452,7 +23399,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Black Trash Bag</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20461,19 +23408,19 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F127" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G127" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H127" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -20487,7 +23434,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cocoa Box</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20496,19 +23443,19 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F128" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G128" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -20522,7 +23469,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Coldbrew Concentrate</t>
+          <t>Cocoa Box</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -20531,19 +23478,19 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F129" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G129" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H129" t="n">
-        <v>2.24</v>
+        <v>3.46</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -20566,19 +23513,19 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E130" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F130" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G130" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H130" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -20601,19 +23548,19 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G131" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H131" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -20636,10 +23583,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F132" t="n">
         <v>0.08</v>
@@ -20648,7 +23595,7 @@
         <v>0.08</v>
       </c>
       <c r="H132" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -20662,7 +23609,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Espresso Trash Bag</t>
+          <t>Wooden Stir Stick</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -20671,10 +23618,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F133" t="n">
         <v>0.08</v>
@@ -20683,7 +23630,7 @@
         <v>0.08</v>
       </c>
       <c r="H133" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="I133" t="n">
         <v>1</v>
@@ -20697,98 +23644,98 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Hand Soap</t>
+          <t>Sanchez (retail)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>40.7</v>
+        <v>39.5</v>
       </c>
       <c r="E134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F134" t="n">
-        <v>0.08</v>
+        <v>3.38</v>
       </c>
       <c r="G134" t="n">
-        <v>0.08</v>
+        <v>1.69</v>
       </c>
       <c r="H134" t="n">
-        <v>3.32</v>
+        <v>1.3</v>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cup Carriers</t>
+          <t>Matcha Drizzle</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>40.7</v>
+        <v>38.6</v>
       </c>
       <c r="E135" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F135" t="n">
-        <v>1.42</v>
+        <v>0.31</v>
       </c>
       <c r="G135" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="H135" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gardena</t>
+          <t>KTOWN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2% Milk</t>
+          <t>Coldbrew Concentrate</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>40.3</v>
+        <v>37.1</v>
       </c>
       <c r="E136" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F136" t="n">
-        <v>0.83</v>
+        <v>0.23</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H136" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="I136" t="n">
         <v>1.5</v>
@@ -20802,7 +23749,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sanchez (retail)</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20811,22 +23758,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>38.2</v>
+        <v>32.9</v>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F137" t="n">
-        <v>3.17</v>
+        <v>0.31</v>
       </c>
       <c r="G137" t="n">
-        <v>1.83</v>
+        <v>0.31</v>
       </c>
       <c r="H137" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>1.692</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -20837,7 +23784,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Matcha Drizzle</t>
+          <t>Decaf Beans</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -20846,19 +23793,19 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="E138" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F138" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="G138" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H138" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="I138" t="n">
         <v>2</v>
@@ -20867,12 +23814,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KTOWN</t>
+          <t>Gardena</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Cup Carriers</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -20881,19 +23828,19 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>28.4</v>
+        <v>29.6</v>
       </c>
       <c r="E139" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F139" t="n">
-        <v>0.33</v>
+        <v>1.54</v>
       </c>
       <c r="G139" t="n">
-        <v>0.25</v>
+        <v>0.92</v>
       </c>
       <c r="H139" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="I139" t="n">
         <v>2</v>
